--- a/data/research/research.xlsx
+++ b/data/research/research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksnyder/Sites/public-domain-books/data/research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E167D97D-A216-EB4B-B3EC-71E385D3B0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9DE35E-947E-B14D-854C-FBF913C17B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1840" yWindow="500" windowWidth="47220" windowHeight="25960" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="1234">
   <si>
     <t>Gen</t>
   </si>
@@ -2288,9 +2288,6 @@
     <t>["Psalm","Pslm","Psm","Pss"]</t>
   </si>
   <si>
-    <t>["The Epistle of Jeremiah","The Letter of Jeremiah","Letter of Jeremiah"]</t>
-  </si>
-  <si>
     <t>["Prv","Pv"]</t>
   </si>
   <si>
@@ -3744,6 +3741,9 @@
   </si>
   <si>
     <t>["Aes"]</t>
+  </si>
+  <si>
+    <t>["Epj","The Epistle of Jeremiah","The Letter of Jeremiah","Letter of Jeremiah"]</t>
   </si>
 </sst>
 </file>
@@ -4238,7 +4238,7 @@
         <v>656</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>587</v>
@@ -4273,7 +4273,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>649</v>
@@ -4285,13 +4285,13 @@
         <v>657</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J2" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>1062</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>1063</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>473</v>
@@ -4322,7 +4322,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>648</v>
@@ -4334,13 +4334,13 @@
         <v>657</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J3" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K3" s="14" t="s">
         <v>1062</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>1063</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>473</v>
@@ -4371,7 +4371,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>650</v>
@@ -4383,13 +4383,13 @@
         <v>657</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J4" s="14" t="s">
         <v>589</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>473</v>
@@ -4420,7 +4420,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>651</v>
@@ -4432,13 +4432,13 @@
         <v>657</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>473</v>
@@ -4469,7 +4469,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>652</v>
@@ -4481,13 +4481,13 @@
         <v>657</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J6" s="14" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K6" s="14" t="s">
         <v>1065</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>1066</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>473</v>
@@ -4519,7 +4519,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>719</v>
@@ -4531,13 +4531,13 @@
         <v>707</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>473</v>
@@ -4569,7 +4569,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>653</v>
@@ -4578,16 +4578,16 @@
         <v>483</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>473</v>
@@ -4619,7 +4619,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>654</v>
@@ -4628,16 +4628,16 @@
         <v>483</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>589</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>473</v>
@@ -4669,7 +4669,7 @@
         <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>738</v>
@@ -4678,16 +4678,16 @@
         <v>483</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>473</v>
@@ -4719,7 +4719,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>739</v>
@@ -4728,16 +4728,16 @@
         <v>483</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>473</v>
@@ -4768,7 +4768,7 @@
         <v>31</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>740</v>
@@ -4780,13 +4780,13 @@
         <v>659</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>473</v>
@@ -4817,7 +4817,7 @@
         <v>34</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>741</v>
@@ -4829,13 +4829,13 @@
         <v>659</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>473</v>
@@ -4866,7 +4866,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>742</v>
@@ -4878,13 +4878,13 @@
         <v>703</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>473</v>
@@ -4915,7 +4915,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>743</v>
@@ -4927,13 +4927,13 @@
         <v>703</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>473</v>
@@ -4965,7 +4965,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>736</v>
@@ -4977,13 +4977,13 @@
         <v>703</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J16" s="14" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K16" s="14" t="s">
         <v>1070</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>1071</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>473</v>
@@ -5015,7 +5015,7 @@
         <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>744</v>
@@ -5024,16 +5024,16 @@
         <v>483</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>473</v>
@@ -5065,7 +5065,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>745</v>
@@ -5074,16 +5074,16 @@
         <v>483</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>473</v>
@@ -5115,7 +5115,7 @@
         <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>746</v>
@@ -5124,16 +5124,16 @@
         <v>483</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>473</v>
@@ -5165,7 +5165,7 @@
         <v>52</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>747</v>
@@ -5174,16 +5174,16 @@
         <v>483</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>473</v>
@@ -5215,25 +5215,25 @@
         <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>473</v>
@@ -5265,7 +5265,7 @@
         <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>737</v>
@@ -5277,13 +5277,13 @@
         <v>680</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J22" s="14" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>1077</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>1078</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>473</v>
@@ -5315,7 +5315,7 @@
         <v>61</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>469</v>
@@ -5327,13 +5327,13 @@
         <v>680</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>473</v>
@@ -5365,10 +5365,10 @@
         <v>64</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>483</v>
@@ -5377,13 +5377,13 @@
         <v>658</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>473</v>
@@ -5415,10 +5415,10 @@
         <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>483</v>
@@ -5427,13 +5427,13 @@
         <v>659</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J25" s="14" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K25" s="14" t="s">
         <v>1080</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>1081</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>473</v>
@@ -5465,10 +5465,10 @@
         <v>70</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>483</v>
@@ -5477,13 +5477,13 @@
         <v>659</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>473</v>
@@ -5515,10 +5515,10 @@
         <v>73</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>483</v>
@@ -5527,13 +5527,13 @@
         <v>660</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J27" s="14" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K27" s="14" t="s">
         <v>1083</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>1084</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>473</v>
@@ -5565,10 +5565,10 @@
         <v>76</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>483</v>
@@ -5577,13 +5577,13 @@
         <v>661</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J28" s="14" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K28" s="14" t="s">
         <v>1085</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>1086</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>473</v>
@@ -5615,25 +5615,25 @@
         <v>79</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>473</v>
@@ -5665,25 +5665,25 @@
         <v>81</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>473</v>
@@ -5715,25 +5715,25 @@
         <v>83</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>473</v>
@@ -5765,25 +5765,25 @@
         <v>86</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>473</v>
@@ -5815,7 +5815,7 @@
         <v>88</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>677</v>
@@ -5824,16 +5824,16 @@
         <v>483</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>473</v>
@@ -5865,25 +5865,25 @@
         <v>91</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>473</v>
@@ -5915,25 +5915,25 @@
         <v>94</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J35" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>1092</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>1093</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>473</v>
@@ -5965,25 +5965,25 @@
         <v>97</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J36" s="14" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K36" s="14" t="s">
         <v>1094</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>1095</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>473</v>
@@ -6015,25 +6015,25 @@
         <v>100</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J37" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K37" s="14" t="s">
         <v>1096</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>1097</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>473</v>
@@ -6065,25 +6065,25 @@
         <v>103</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J38" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K38" s="14" t="s">
         <v>1098</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>1099</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>473</v>
@@ -6115,25 +6115,25 @@
         <v>106</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>473</v>
@@ -6165,25 +6165,25 @@
         <v>109</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>473</v>
@@ -6226,13 +6226,13 @@
         <v>666</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J41" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K41" s="14" t="s">
         <v>1101</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>1102</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>473</v>
@@ -6275,13 +6275,13 @@
         <v>665</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J42" s="14" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K42" s="14" t="s">
         <v>1103</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>1104</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>473</v>
@@ -6324,13 +6324,13 @@
         <v>664</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J43" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K43" s="14" t="s">
         <v>1105</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>1106</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>473</v>
@@ -6373,13 +6373,13 @@
         <v>662</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>473</v>
@@ -6413,22 +6413,22 @@
         <v>454</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H45" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J45" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K45" s="14" t="s">
         <v>1105</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>1106</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>473</v>
@@ -6462,7 +6462,7 @@
         <v>455</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>483</v>
@@ -6471,13 +6471,13 @@
         <v>663</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J46" s="14" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K46" s="14" t="s">
         <v>1108</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>1109</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>473</v>
@@ -6511,7 +6511,7 @@
         <v>455</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>483</v>
@@ -6520,13 +6520,13 @@
         <v>663</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J47" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K47" s="14" t="s">
         <v>1110</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>1111</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>473</v>
@@ -6560,7 +6560,7 @@
         <v>455</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>483</v>
@@ -6569,13 +6569,13 @@
         <v>663</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J48" s="14" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K48" s="14" t="s">
         <v>1112</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>1113</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>473</v>
@@ -6609,7 +6609,7 @@
         <v>455</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>483</v>
@@ -6618,13 +6618,13 @@
         <v>663</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>473</v>
@@ -6658,7 +6658,7 @@
         <v>455</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>483</v>
@@ -6667,13 +6667,13 @@
         <v>663</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>473</v>
@@ -6707,7 +6707,7 @@
         <v>455</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>483</v>
@@ -6716,13 +6716,13 @@
         <v>663</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J51" s="14" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K51" s="14" t="s">
         <v>1116</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>1117</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>473</v>
@@ -6756,7 +6756,7 @@
         <v>455</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>483</v>
@@ -6765,13 +6765,13 @@
         <v>663</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>473</v>
@@ -6805,7 +6805,7 @@
         <v>455</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>483</v>
@@ -6814,13 +6814,13 @@
         <v>663</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J53" s="14" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K53" s="14" t="s">
         <v>1119</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>1120</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>473</v>
@@ -6854,7 +6854,7 @@
         <v>455</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>483</v>
@@ -6863,13 +6863,13 @@
         <v>663</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>473</v>
@@ -6903,7 +6903,7 @@
         <v>455</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>483</v>
@@ -6912,13 +6912,13 @@
         <v>663</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>473</v>
@@ -6952,7 +6952,7 @@
         <v>455</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>483</v>
@@ -6961,13 +6961,13 @@
         <v>663</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>473</v>
@@ -7001,7 +7001,7 @@
         <v>455</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>483</v>
@@ -7010,13 +7010,13 @@
         <v>663</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>473</v>
@@ -7050,7 +7050,7 @@
         <v>455</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>483</v>
@@ -7059,13 +7059,13 @@
         <v>663</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J58" s="14" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K58" s="14" t="s">
         <v>1116</v>
-      </c>
-      <c r="K58" s="14" t="s">
-        <v>1117</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>473</v>
@@ -7108,13 +7108,13 @@
         <v>677</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>473</v>
@@ -7148,22 +7148,22 @@
         <v>454</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>483</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>473</v>
@@ -7197,7 +7197,7 @@
         <v>454</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>483</v>
@@ -7206,13 +7206,13 @@
         <v>668</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>473</v>
@@ -7246,7 +7246,7 @@
         <v>454</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>483</v>
@@ -7255,13 +7255,13 @@
         <v>668</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>473</v>
@@ -7295,7 +7295,7 @@
         <v>454</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>483</v>
@@ -7304,13 +7304,13 @@
         <v>669</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>473</v>
@@ -7344,7 +7344,7 @@
         <v>454</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>483</v>
@@ -7353,13 +7353,13 @@
         <v>669</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>473</v>
@@ -7393,7 +7393,7 @@
         <v>454</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>483</v>
@@ -7402,13 +7402,13 @@
         <v>669</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>473</v>
@@ -7442,7 +7442,7 @@
         <v>454</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>483</v>
@@ -7451,13 +7451,13 @@
         <v>683</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>473</v>
@@ -7491,7 +7491,7 @@
         <v>454</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>483</v>
@@ -7500,13 +7500,13 @@
         <v>670</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J67" s="14" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K67" s="14" t="s">
         <v>1124</v>
-      </c>
-      <c r="K67" s="14" t="s">
-        <v>1125</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>473</v>
@@ -7550,13 +7550,13 @@
         <v>682</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J68" s="14" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K68" s="14" t="s">
         <v>1152</v>
-      </c>
-      <c r="K68" s="14" t="s">
-        <v>1153</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>473</v>
@@ -7600,13 +7600,13 @@
         <v>681</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>473</v>
@@ -7640,16 +7640,16 @@
         <v>677</v>
       </c>
       <c r="H70" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J70" s="14" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K70" s="14" t="s">
         <v>1155</v>
-      </c>
-      <c r="K70" s="14" t="s">
-        <v>1156</v>
       </c>
       <c r="L70" t="s">
         <v>473</v>
@@ -7683,22 +7683,22 @@
         <v>456</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>482</v>
       </c>
       <c r="H71" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J71" s="14" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K71" s="14" t="s">
         <v>1157</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>1158</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>473</v>
@@ -7741,13 +7741,13 @@
         <v>680</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>473</v>
@@ -7787,16 +7787,16 @@
         <v>482</v>
       </c>
       <c r="H73" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>473</v>
@@ -7836,16 +7836,16 @@
         <v>482</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J74" s="16" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K74" s="16" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>473</v>
@@ -7863,50 +7863,52 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="A75" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="F75" t="s">
-        <v>748</v>
-      </c>
-      <c r="G75" s="7"/>
-      <c r="H75" t="s">
+      <c r="F75" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="I75" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="J75" s="14" t="s">
-        <v>1085</v>
-      </c>
-      <c r="K75" s="14" t="s">
-        <v>1075</v>
-      </c>
-      <c r="L75" t="s">
-        <v>473</v>
-      </c>
-      <c r="M75" t="s">
-        <v>477</v>
-      </c>
-      <c r="N75" t="str">
-        <f t="shared" si="6"/>
-        <v>false</v>
+      <c r="I75" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="N75" s="3" t="str">
+        <f>"true"</f>
+        <v>true</v>
       </c>
       <c r="O75" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>{ "workOsisID": "", "bookName": "Epistle of Jeremiah", "bookSubtitle": "The Epistle of Jeremiah", "bookOsisID": "EpJer", "paratext": "LJE", "groups": ["Deuterocannon", "Apocrypha"], "aliases": ["The Epistle of Jeremiah","The Letter of Jeremiah","Letter of Jeremiah"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jeremiah"], "dateEarliest": "-0200-01-01", "dateLatest": "-0100-12-31", "hasData": false, "traditions": ["roman catholic","eastern orthodox","oriental orthodox","ethiopian orthodox"] },</v>
+        <v>{ "workOsisID": "KJVA", "bookName": "Epistle of Jeremiah", "bookSubtitle": "The Epistle of Jeremiah", "bookOsisID": "EpJer", "paratext": "LJE", "groups": ["Deuterocannon", "Apocrypha"], "aliases": ["Epj","The Epistle of Jeremiah","The Letter of Jeremiah","Letter of Jeremiah"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jeremiah"], "dateEarliest": "-0200-01-01", "dateLatest": "-0100-12-31", "hasData": true, "traditions": ["roman catholic","eastern orthodox","oriental orthodox","ethiopian orthodox"] },</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
@@ -7929,13 +7931,13 @@
         <v>661</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="K76" s="14" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="L76" t="s">
         <v>473</v>
@@ -7969,13 +7971,13 @@
         <v>661</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K77" s="14" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L77" t="s">
         <v>473</v>
@@ -8009,7 +8011,7 @@
         <v>456</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>482</v>
@@ -8018,13 +8020,13 @@
         <v>679</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J78" s="14" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K78" s="14" t="s">
         <v>1164</v>
-      </c>
-      <c r="K78" s="14" t="s">
-        <v>1165</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>473</v>
@@ -8067,13 +8069,13 @@
         <v>661</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K79" s="14" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>473</v>
@@ -8114,13 +8116,13 @@
         <v>661</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J80" s="16" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K80" s="16" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>473</v>
@@ -8129,12 +8131,12 @@
         <v>477</v>
       </c>
       <c r="N80" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>false</v>
+        <f>"true"</f>
+        <v>true</v>
       </c>
       <c r="O80" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>{ "workOsisID": "KJVA", "bookName": "Bel and the Dragon", "bookSubtitle": "", "bookOsisID": "Bel", "paratext": "BEL", "groups": ["Deuterocannon", "Apocrypha"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Daniel"], "dateEarliest": "-0100-01-01", "dateLatest": "-0050-12-31", "hasData": false, "traditions": ["roman catholic","eastern orthodox","oriental orthodox","ethiopian orthodox"] },</v>
+        <v>{ "workOsisID": "KJVA", "bookName": "Bel and the Dragon", "bookSubtitle": "", "bookOsisID": "Bel", "paratext": "BEL", "groups": ["Deuterocannon", "Apocrypha"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Daniel"], "dateEarliest": "-0100-01-01", "dateLatest": "-0050-12-31", "hasData": true, "traditions": ["roman catholic","eastern orthodox","oriental orthodox","ethiopian orthodox"] },</v>
       </c>
     </row>
     <row r="81" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -8154,7 +8156,7 @@
         <v>456</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>482</v>
@@ -8163,13 +8165,13 @@
         <v>677</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K81" s="14" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>473</v>
@@ -8203,7 +8205,7 @@
         <v>456</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>482</v>
@@ -8212,13 +8214,13 @@
         <v>677</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J82" s="14" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K82" s="14" t="s">
         <v>1167</v>
-      </c>
-      <c r="K82" s="14" t="s">
-        <v>1168</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>473</v>
@@ -8258,13 +8260,13 @@
         <v>677</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K83" s="14" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L83" t="s">
         <v>473</v>
@@ -8304,13 +8306,13 @@
         <v>677</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J84" s="14" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K84" s="14" t="s">
         <v>1127</v>
-      </c>
-      <c r="K84" s="14" t="s">
-        <v>1128</v>
       </c>
       <c r="L84" t="s">
         <v>473</v>
@@ -8353,13 +8355,13 @@
         <v>678</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>473</v>
@@ -8393,7 +8395,7 @@
         <v>456</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>482</v>
@@ -8402,13 +8404,13 @@
         <v>703</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>473</v>
@@ -8442,7 +8444,7 @@
         <v>456</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>482</v>
@@ -8451,13 +8453,13 @@
         <v>703</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>473</v>
@@ -8491,16 +8493,16 @@
         <v>677</v>
       </c>
       <c r="H88" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L88" t="s">
         <v>473</v>
@@ -8534,19 +8536,19 @@
         <v>677</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H89" t="s">
         <v>677</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L89" t="s">
         <v>473</v>
@@ -8580,19 +8582,19 @@
         <v>677</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H90" t="s">
         <v>680</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="L90" t="s">
         <v>473</v>
@@ -8626,19 +8628,19 @@
         <v>677</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H91" t="s">
         <v>707</v>
       </c>
       <c r="I91" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L91" t="s">
         <v>473</v>
@@ -8672,19 +8674,19 @@
         <v>677</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H92" t="s">
         <v>677</v>
       </c>
       <c r="I92" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L92" t="s">
         <v>473</v>
@@ -8718,19 +8720,19 @@
         <v>677</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H93" t="s">
         <v>682</v>
       </c>
       <c r="I93" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="L93" t="s">
         <v>473</v>
@@ -8764,19 +8766,19 @@
         <v>677</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H94" t="s">
         <v>661</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="L94" t="s">
         <v>473</v>
@@ -8810,19 +8812,19 @@
         <v>677</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H95" t="s">
         <v>661</v>
       </c>
       <c r="I95" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L95" t="s">
         <v>473</v>
@@ -8856,19 +8858,19 @@
         <v>677</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H96" t="s">
         <v>661</v>
       </c>
       <c r="I96" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K96" s="14" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="L96" t="s">
         <v>473</v>
@@ -8902,7 +8904,7 @@
         <v>457</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>482</v>
@@ -8911,13 +8913,13 @@
         <v>663</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L97" s="3" t="s">
         <v>473</v>
@@ -8951,19 +8953,19 @@
         <v>677</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H98" t="s">
         <v>703</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L98" t="s">
         <v>473</v>
@@ -8997,19 +8999,19 @@
         <v>722</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H99" t="s">
         <v>703</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L99" t="s">
         <v>473</v>
@@ -9043,19 +9045,19 @@
         <v>677</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H100" t="s">
         <v>703</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L100" t="s">
         <v>473</v>
@@ -9089,19 +9091,19 @@
         <v>677</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H101" t="s">
         <v>680</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L101" t="s">
         <v>473</v>
@@ -9135,19 +9137,19 @@
         <v>677</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H102" t="s">
         <v>659</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K102" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L102" t="s">
         <v>473</v>
@@ -9175,25 +9177,25 @@
         <v>278</v>
       </c>
       <c r="E103" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F103" t="s">
         <v>723</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H103" t="s">
         <v>704</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K103" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L103" t="s">
         <v>473</v>
@@ -9221,7 +9223,7 @@
         <v>281</v>
       </c>
       <c r="E104" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F104" t="s">
         <v>677</v>
@@ -9230,13 +9232,13 @@
         <v>657</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J104" s="14" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K104" s="14" t="s">
         <v>1164</v>
-      </c>
-      <c r="K104" s="14" t="s">
-        <v>1165</v>
       </c>
       <c r="L104" t="s">
         <v>473</v>
@@ -9264,22 +9266,22 @@
         <v>284</v>
       </c>
       <c r="E105" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F105" t="s">
         <v>724</v>
       </c>
       <c r="H105" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="K105" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L105" t="s">
         <v>473</v>
@@ -9307,22 +9309,22 @@
         <v>286</v>
       </c>
       <c r="E106" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F106" t="s">
         <v>677</v>
       </c>
       <c r="H106" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K106" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L106" t="s">
         <v>473</v>
@@ -9350,22 +9352,22 @@
         <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F107" t="s">
         <v>677</v>
       </c>
       <c r="H107" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K107" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="L107" t="s">
         <v>473</v>
@@ -9393,22 +9395,22 @@
         <v>290</v>
       </c>
       <c r="E108" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F108" t="s">
         <v>677</v>
       </c>
       <c r="H108" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="K108" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L108" t="s">
         <v>473</v>
@@ -9436,7 +9438,7 @@
         <v>292</v>
       </c>
       <c r="E109" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F109" t="s">
         <v>725</v>
@@ -9445,13 +9447,13 @@
         <v>677</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="K109" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L109" t="s">
         <v>473</v>
@@ -9476,7 +9478,7 @@
         <v>293</v>
       </c>
       <c r="E110" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F110" t="s">
         <v>726</v>
@@ -9485,13 +9487,13 @@
         <v>659</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K110" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L110" t="s">
         <v>473</v>
@@ -9516,7 +9518,7 @@
         <v>295</v>
       </c>
       <c r="E111" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F111" t="s">
         <v>727</v>
@@ -9525,13 +9527,13 @@
         <v>697</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K111" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L111" t="s">
         <v>473</v>
@@ -9559,22 +9561,22 @@
         <v>297</v>
       </c>
       <c r="E112" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F112" t="s">
         <v>677</v>
       </c>
       <c r="H112" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K112" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L112" t="s">
         <v>473</v>
@@ -9602,7 +9604,7 @@
         <v>300</v>
       </c>
       <c r="E113" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F113" t="s">
         <v>677</v>
@@ -9611,13 +9613,13 @@
         <v>663</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K113" s="14" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L113" t="s">
         <v>473</v>
@@ -9645,22 +9647,22 @@
         <v>302</v>
       </c>
       <c r="E114" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F114" t="s">
         <v>677</v>
       </c>
       <c r="H114" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J114" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K114" s="14" t="s">
         <v>1159</v>
-      </c>
-      <c r="K114" s="14" t="s">
-        <v>1160</v>
       </c>
       <c r="L114" t="s">
         <v>473</v>
@@ -9688,7 +9690,7 @@
         <v>304</v>
       </c>
       <c r="E115" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F115" t="s">
         <v>677</v>
@@ -9697,13 +9699,13 @@
         <v>705</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="K115" s="14" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L115" t="s">
         <v>473</v>
@@ -9731,7 +9733,7 @@
         <v>306</v>
       </c>
       <c r="E116" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F116" t="s">
         <v>677</v>
@@ -9740,13 +9742,13 @@
         <v>706</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K116" s="14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L116" t="s">
         <v>473</v>
@@ -9771,22 +9773,22 @@
         <v>307</v>
       </c>
       <c r="E117" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F117" t="s">
         <v>677</v>
       </c>
       <c r="H117" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K117" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L117" t="s">
         <v>473</v>
@@ -9811,7 +9813,7 @@
         <v>309</v>
       </c>
       <c r="E118" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F118" t="s">
         <v>677</v>
@@ -9820,16 +9822,16 @@
         <v>309</v>
       </c>
       <c r="H118" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K118" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L118" t="s">
         <v>473</v>
@@ -9854,7 +9856,7 @@
         <v>532</v>
       </c>
       <c r="E119" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F119" t="s">
         <v>677</v>
@@ -9866,13 +9868,13 @@
         <v>684</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K119" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L119" t="s">
         <v>473</v>
@@ -9897,7 +9899,7 @@
         <v>533</v>
       </c>
       <c r="E120" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F120" t="s">
         <v>677</v>
@@ -9909,13 +9911,13 @@
         <v>685</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K120" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L120" t="s">
         <v>473</v>
@@ -9940,7 +9942,7 @@
         <v>534</v>
       </c>
       <c r="E121" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F121" t="s">
         <v>677</v>
@@ -9952,13 +9954,13 @@
         <v>686</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K121" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L121" t="s">
         <v>473</v>
@@ -9983,7 +9985,7 @@
         <v>535</v>
       </c>
       <c r="E122" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F122" t="s">
         <v>677</v>
@@ -9995,13 +9997,13 @@
         <v>687</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K122" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L122" t="s">
         <v>473</v>
@@ -10026,7 +10028,7 @@
         <v>536</v>
       </c>
       <c r="E123" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F123" t="s">
         <v>677</v>
@@ -10038,13 +10040,13 @@
         <v>688</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K123" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L123" t="s">
         <v>473</v>
@@ -10069,7 +10071,7 @@
         <v>537</v>
       </c>
       <c r="E124" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F124" t="s">
         <v>677</v>
@@ -10081,13 +10083,13 @@
         <v>689</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K124" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L124" t="s">
         <v>473</v>
@@ -10112,7 +10114,7 @@
         <v>538</v>
       </c>
       <c r="E125" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F125" t="s">
         <v>677</v>
@@ -10124,13 +10126,13 @@
         <v>690</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K125" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L125" t="s">
         <v>473</v>
@@ -10155,7 +10157,7 @@
         <v>539</v>
       </c>
       <c r="E126" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F126" t="s">
         <v>677</v>
@@ -10167,13 +10169,13 @@
         <v>691</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K126" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L126" t="s">
         <v>473</v>
@@ -10198,7 +10200,7 @@
         <v>540</v>
       </c>
       <c r="E127" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F127" t="s">
         <v>677</v>
@@ -10210,13 +10212,13 @@
         <v>692</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K127" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L127" t="s">
         <v>473</v>
@@ -10241,7 +10243,7 @@
         <v>541</v>
       </c>
       <c r="E128" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F128" t="s">
         <v>677</v>
@@ -10253,13 +10255,13 @@
         <v>693</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K128" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L128" t="s">
         <v>473</v>
@@ -10284,7 +10286,7 @@
         <v>542</v>
       </c>
       <c r="E129" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F129" t="s">
         <v>677</v>
@@ -10296,13 +10298,13 @@
         <v>694</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K129" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L129" t="s">
         <v>473</v>
@@ -10327,7 +10329,7 @@
         <v>543</v>
       </c>
       <c r="E130" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F130" t="s">
         <v>677</v>
@@ -10339,13 +10341,13 @@
         <v>695</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K130" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L130" t="s">
         <v>473</v>
@@ -10383,13 +10385,13 @@
         <v>696</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="K131" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L131" t="s">
         <v>473</v>
@@ -10426,13 +10428,13 @@
         <v>696</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J132" s="14" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K132" s="14" t="s">
         <v>1101</v>
-      </c>
-      <c r="K132" s="14" t="s">
-        <v>1102</v>
       </c>
       <c r="L132" t="s">
         <v>473</v>
@@ -10466,16 +10468,16 @@
         <v>442</v>
       </c>
       <c r="H133" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="K133" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L133" t="s">
         <v>473</v>
@@ -10509,13 +10511,13 @@
         <v>697</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J134" s="14" t="s">
+        <v>1174</v>
+      </c>
+      <c r="K134" s="14" t="s">
         <v>1175</v>
-      </c>
-      <c r="K134" s="14" t="s">
-        <v>1176</v>
       </c>
       <c r="L134" t="s">
         <v>473</v>
@@ -10552,19 +10554,19 @@
         <v>677</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H135" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="K135" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L135" t="s">
         <v>473</v>
@@ -10601,19 +10603,19 @@
         <v>677</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H136" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K136" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L136" t="s">
         <v>473</v>
@@ -10647,19 +10649,19 @@
         <v>677</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H137" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J137" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K137" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K137" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L137" t="s">
         <v>473</v>
@@ -10693,19 +10695,19 @@
         <v>677</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H138" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J138" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K138" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K138" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L138" t="s">
         <v>473</v>
@@ -10739,19 +10741,19 @@
         <v>677</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H139" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J139" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K139" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K139" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L139" t="s">
         <v>473</v>
@@ -10785,19 +10787,19 @@
         <v>677</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H140" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J140" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K140" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K140" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L140" t="s">
         <v>473</v>
@@ -10831,19 +10833,19 @@
         <v>677</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H141" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J141" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K141" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K141" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L141" t="s">
         <v>473</v>
@@ -10877,19 +10879,19 @@
         <v>677</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H142" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J142" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K142" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K142" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L142" t="s">
         <v>473</v>
@@ -10923,19 +10925,19 @@
         <v>677</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H143" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J143" s="14" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K143" s="14" t="s">
         <v>1178</v>
-      </c>
-      <c r="K143" s="14" t="s">
-        <v>1179</v>
       </c>
       <c r="L143" t="s">
         <v>473</v>
@@ -10969,19 +10971,19 @@
         <v>677</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H144" t="s">
         <v>698</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J144" s="14" t="s">
+        <v>1179</v>
+      </c>
+      <c r="K144" s="14" t="s">
         <v>1180</v>
-      </c>
-      <c r="K144" s="14" t="s">
-        <v>1181</v>
       </c>
       <c r="L144" t="s">
         <v>473</v>
@@ -11015,19 +11017,19 @@
         <v>677</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H145" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J145" s="14" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K145" s="14" t="s">
         <v>1182</v>
-      </c>
-      <c r="K145" s="14" t="s">
-        <v>1183</v>
       </c>
       <c r="L145" t="s">
         <v>473</v>
@@ -11070,13 +11072,13 @@
         <v>677</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="K146" s="14" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L146" s="3" t="s">
         <v>473</v>
@@ -11110,19 +11112,19 @@
         <v>677</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H147" t="s">
         <v>699</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J147" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K147" s="14" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L147" t="s">
         <v>473</v>
@@ -11159,19 +11161,19 @@
         <v>677</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H148" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J148" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K148" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L148" t="s">
         <v>473</v>
@@ -11205,19 +11207,19 @@
         <v>677</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H149" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J149" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K149" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L149" t="s">
         <v>473</v>
@@ -11251,19 +11253,19 @@
         <v>677</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H150" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J150" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K150" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L150" t="s">
         <v>473</v>
@@ -11297,19 +11299,19 @@
         <v>677</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H151" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J151" s="14" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K151" s="14" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L151" t="s">
         <v>473</v>
@@ -11343,19 +11345,19 @@
         <v>677</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H152" t="s">
         <v>677</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K152" s="14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L152" t="s">
         <v>473</v>
@@ -11387,19 +11389,19 @@
         <v>677</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H153" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="J153" s="14" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K153" s="14" t="s">
         <v>1186</v>
-      </c>
-      <c r="K153" s="14" t="s">
-        <v>1187</v>
       </c>
       <c r="L153" t="s">
         <v>473</v>
@@ -11433,19 +11435,19 @@
         <v>677</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H154" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K154" s="14" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="L154" t="s">
         <v>473</v>
@@ -11476,19 +11478,19 @@
         <v>677</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H155" t="s">
         <v>677</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J155" s="14" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K155" s="14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="L155" t="s">
         <v>473</v>
@@ -11522,19 +11524,19 @@
         <v>677</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H156" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J156" s="14" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K156" s="14" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="L156" t="s">
         <v>473</v>
@@ -11565,19 +11567,19 @@
         <v>441</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H157" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J157" s="14" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K157" s="14" t="s">
         <v>1132</v>
-      </c>
-      <c r="K157" s="14" t="s">
-        <v>1133</v>
       </c>
       <c r="L157" t="s">
         <v>473</v>
@@ -11611,19 +11613,19 @@
         <v>677</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>677</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J158" s="14" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K158" s="14" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="L158" t="s">
         <v>473</v>
@@ -11660,7 +11662,7 @@
         <v>671</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J159" s="15" t="s">
         <v>589</v>
@@ -11703,7 +11705,7 @@
         <v>671</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J160" s="15" t="s">
         <v>591</v>
@@ -11749,7 +11751,7 @@
         <v>672</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J161" s="15" t="s">
         <v>593</v>
@@ -11792,7 +11794,7 @@
         <v>700</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J162" s="15" t="s">
         <v>595</v>
@@ -11835,7 +11837,7 @@
         <v>701</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J163" s="15" t="s">
         <v>596</v>
@@ -11878,7 +11880,7 @@
         <v>702</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J164" s="15" t="s">
         <v>598</v>
@@ -11921,7 +11923,7 @@
         <v>673</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J165" s="15" t="s">
         <v>600</v>
@@ -11964,7 +11966,7 @@
         <v>673</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J166" s="15" t="s">
         <v>599</v>
@@ -12010,7 +12012,7 @@
         <v>673</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J167" s="15" t="s">
         <v>601</v>
@@ -12053,7 +12055,7 @@
         <v>673</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J168" s="15" t="s">
         <v>602</v>
@@ -12099,7 +12101,7 @@
         <v>673</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J169" s="15" t="s">
         <v>604</v>
@@ -12145,7 +12147,7 @@
         <v>673</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J170" s="15" t="s">
         <v>605</v>
@@ -12188,7 +12190,7 @@
         <v>673</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J171" s="15" t="s">
         <v>606</v>
@@ -12234,7 +12236,7 @@
         <v>673</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J172" s="15" t="s">
         <v>608</v>
@@ -12277,7 +12279,7 @@
         <v>673</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J173" s="15" t="s">
         <v>610</v>
@@ -12323,13 +12325,13 @@
         <v>657</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J174" s="12" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K174" s="12" t="s">
         <v>1214</v>
-      </c>
-      <c r="K174" s="12" t="s">
-        <v>1215</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>473</v>
@@ -12369,13 +12371,13 @@
         <v>674</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J175" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K175" s="12" t="s">
         <v>1216</v>
-      </c>
-      <c r="K175" s="12" t="s">
-        <v>1217</v>
       </c>
       <c r="L175" s="3" t="s">
         <v>473</v>
@@ -12415,13 +12417,13 @@
         <v>675</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="M176" s="3" t="s">
         <v>478</v>
@@ -12458,13 +12460,13 @@
         <v>675</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J177" s="12" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K177" s="12" t="s">
         <v>1219</v>
-      </c>
-      <c r="K177" s="12" t="s">
-        <v>1220</v>
       </c>
       <c r="M177" s="3" t="s">
         <v>477</v>
@@ -12501,13 +12503,13 @@
         <v>666</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J178" s="12" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K178" s="12" t="s">
         <v>1221</v>
-      </c>
-      <c r="K178" s="12" t="s">
-        <v>1222</v>
       </c>
       <c r="M178" s="3" t="s">
         <v>477</v>
@@ -12544,13 +12546,13 @@
         <v>675</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J179" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K179" s="15" t="s">
         <v>1209</v>
-      </c>
-      <c r="K179" s="15" t="s">
-        <v>1210</v>
       </c>
       <c r="L179" s="3" t="s">
         <v>474</v>
@@ -12572,13 +12574,13 @@
         <v>640</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="J180" s="14" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K180" s="14" t="s">
         <v>1134</v>
-      </c>
-      <c r="K180" s="14" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.2">
@@ -12586,13 +12588,13 @@
         <v>611</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="J181" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K181" s="14" t="s">
         <v>1136</v>
-      </c>
-      <c r="K181" s="14" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.2">
@@ -12600,13 +12602,13 @@
         <v>612</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J182" s="14" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="K182" s="14" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.2">
@@ -12614,13 +12616,13 @@
         <v>613</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J183" s="14" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K183" s="14" t="s">
         <v>1189</v>
-      </c>
-      <c r="K183" s="14" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.2">
@@ -12628,13 +12630,13 @@
         <v>614</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="K184" s="14" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.2">
@@ -12642,13 +12644,13 @@
         <v>615</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J185" s="14" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K185" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.2">
@@ -12656,13 +12658,13 @@
         <v>616</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K186" s="14" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.2">
@@ -12670,13 +12672,13 @@
         <v>617</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="K187" s="14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.2">
@@ -12684,13 +12686,13 @@
         <v>618</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J188" s="14" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K188" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.2">
@@ -12698,13 +12700,13 @@
         <v>619</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J189" s="14" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K189" s="14" t="s">
         <v>1077</v>
-      </c>
-      <c r="K189" s="14" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.2">
@@ -12712,13 +12714,13 @@
         <v>620</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K190" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.2">
@@ -12726,13 +12728,13 @@
         <v>621</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J191" s="14" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K191" s="14" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.2">
@@ -12740,13 +12742,13 @@
         <v>622</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J192" s="14" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K192" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
@@ -12754,13 +12756,13 @@
         <v>623</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K193" s="14" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
@@ -12768,13 +12770,13 @@
         <v>624</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="K194" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
@@ -12782,13 +12784,13 @@
         <v>625</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="J195" s="14" t="s">
         <v>589</v>
       </c>
       <c r="K195" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
@@ -12796,13 +12798,13 @@
         <v>626</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K196" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
@@ -12810,13 +12812,13 @@
         <v>627</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K197" s="14" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
@@ -12824,13 +12826,13 @@
         <v>628</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="K198" s="14" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
@@ -12838,13 +12840,13 @@
         <v>629</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="J199" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K199" s="14" t="s">
         <v>1193</v>
-      </c>
-      <c r="K199" s="14" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
@@ -12852,13 +12854,13 @@
         <v>630</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K200" s="14" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
@@ -12866,13 +12868,13 @@
         <v>631</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="J201" s="14" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K201" s="14" t="s">
         <v>1196</v>
-      </c>
-      <c r="K201" s="14" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.2">
@@ -12880,13 +12882,13 @@
         <v>632</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="J202" s="14" t="s">
+        <v>1197</v>
+      </c>
+      <c r="K202" s="14" t="s">
         <v>1198</v>
-      </c>
-      <c r="K202" s="14" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.2">
@@ -12894,13 +12896,13 @@
         <v>633</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="J203" s="14" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K203" s="14" t="s">
         <v>1200</v>
-      </c>
-      <c r="K203" s="14" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.2">
@@ -12908,13 +12910,13 @@
         <v>634</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="K204" s="14" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.2">
@@ -12922,13 +12924,13 @@
         <v>635</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="K205" s="14" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.2">
@@ -12936,13 +12938,13 @@
         <v>636</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="J206" s="14" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K206" s="14" t="s">
         <v>1204</v>
-      </c>
-      <c r="K206" s="14" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.2">
@@ -12950,13 +12952,13 @@
         <v>637</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="J207" s="14" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K207" s="14" t="s">
         <v>1206</v>
-      </c>
-      <c r="K207" s="14" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.2">
@@ -12964,13 +12966,13 @@
         <v>638</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="J208" s="14" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="K208" s="14" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.2">
@@ -12978,13 +12980,13 @@
         <v>639</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K209" s="14" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
@@ -13190,16 +13192,16 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
+        <v>755</v>
+      </c>
+      <c r="C9" t="s">
+        <v>751</v>
+      </c>
+      <c r="D9" t="s">
         <v>756</v>
       </c>
-      <c r="C9" t="s">
-        <v>752</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>757</v>
-      </c>
-      <c r="E9" t="s">
-        <v>758</v>
       </c>
       <c r="H9" t="str">
         <f>"false"</f>
@@ -13223,12 +13225,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -13246,12 +13248,12 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -13259,10 +13261,10 @@
         <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -13275,7 +13277,7 @@
         <v>379</v>
       </c>
       <c r="E5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -13288,7 +13290,7 @@
         <v>197</v>
       </c>
       <c r="E7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -13301,7 +13303,7 @@
         <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -13314,7 +13316,7 @@
         <v>563</v>
       </c>
       <c r="E11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -13327,7 +13329,7 @@
         <v>210</v>
       </c>
       <c r="E13" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -13340,7 +13342,7 @@
         <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -13353,7 +13355,7 @@
         <v>221</v>
       </c>
       <c r="E17" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
@@ -13366,7 +13368,7 @@
         <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
@@ -13379,7 +13381,7 @@
         <v>233</v>
       </c>
       <c r="E21" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
@@ -13387,13 +13389,13 @@
         <v>236</v>
       </c>
       <c r="P22" t="s">
+        <v>866</v>
+      </c>
+      <c r="Q22" t="s">
         <v>867</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>868</v>
-      </c>
-      <c r="R22" t="s">
-        <v>869</v>
       </c>
       <c r="S22" t="str">
         <f>SUBSTITUTE(Q22," ", "")</f>
@@ -13404,7 +13406,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U22" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
@@ -13412,22 +13414,22 @@
         <v>239</v>
       </c>
       <c r="E23" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>822</v>
-      </c>
       <c r="P23" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Q23" t="s">
+        <v>867</v>
+      </c>
+      <c r="R23" t="s">
         <v>868</v>
-      </c>
-      <c r="R23" t="s">
-        <v>869</v>
       </c>
       <c r="S23" t="str">
         <f t="shared" ref="S23:S86" si="0">SUBSTITUTE(Q23," ", "")</f>
@@ -13438,7 +13440,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U23" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -13452,19 +13454,19 @@
         <v>682</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>822</v>
-      </c>
       <c r="P24" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q24" t="s">
         <v>873</v>
       </c>
-      <c r="Q24" t="s">
-        <v>874</v>
-      </c>
       <c r="R24" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S24" t="str">
         <f t="shared" si="0"/>
@@ -13475,7 +13477,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -13495,13 +13497,13 @@
         <v>657</v>
       </c>
       <c r="P25" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q25" t="s">
         <v>876</v>
       </c>
-      <c r="Q25" t="s">
-        <v>877</v>
-      </c>
       <c r="R25" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S25" t="str">
         <f t="shared" si="0"/>
@@ -13512,7 +13514,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U25" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.2">
@@ -13523,7 +13525,7 @@
         <v>379</v>
       </c>
       <c r="G26" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I26" t="s">
         <v>4</v>
@@ -13532,13 +13534,13 @@
         <v>657</v>
       </c>
       <c r="P26" t="s">
+        <v>878</v>
+      </c>
+      <c r="Q26" t="s">
         <v>879</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>880</v>
-      </c>
-      <c r="R26" t="s">
-        <v>881</v>
       </c>
       <c r="S26" t="str">
         <f t="shared" si="0"/>
@@ -13549,7 +13551,7 @@
         <v>-0500-12-31</v>
       </c>
       <c r="U26" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
@@ -13560,7 +13562,7 @@
         <v>194</v>
       </c>
       <c r="G27" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I27" t="s">
         <v>7</v>
@@ -13569,13 +13571,13 @@
         <v>657</v>
       </c>
       <c r="P27" t="s">
+        <v>882</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>879</v>
+      </c>
+      <c r="R27" t="s">
         <v>883</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>880</v>
-      </c>
-      <c r="R27" t="s">
-        <v>884</v>
       </c>
       <c r="S27" t="str">
         <f t="shared" si="0"/>
@@ -13586,7 +13588,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U27" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
@@ -13606,13 +13608,13 @@
         <v>657</v>
       </c>
       <c r="P28" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="Q28" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R28" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S28" t="str">
         <f t="shared" si="0"/>
@@ -13623,7 +13625,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U28" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
@@ -13643,13 +13645,13 @@
         <v>657</v>
       </c>
       <c r="P29" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>873</v>
+      </c>
+      <c r="R29" t="s">
         <v>888</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>874</v>
-      </c>
-      <c r="R29" t="s">
-        <v>889</v>
       </c>
       <c r="S29" t="str">
         <f t="shared" si="0"/>
@@ -13660,7 +13662,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U29" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
@@ -13671,7 +13673,7 @@
         <v>200</v>
       </c>
       <c r="G30" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I30" t="s">
         <v>16</v>
@@ -13680,13 +13682,13 @@
         <v>707</v>
       </c>
       <c r="P30" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Q30" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R30" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S30" t="str">
         <f t="shared" si="0"/>
@@ -13697,7 +13699,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U30" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.2">
@@ -13708,22 +13710,22 @@
         <v>203</v>
       </c>
       <c r="G31" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P31" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="Q31" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R31" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S31" t="str">
         <f t="shared" si="0"/>
@@ -13734,7 +13736,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U31" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
@@ -13751,16 +13753,16 @@
         <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P32" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="Q32" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R32" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S32" t="str">
         <f t="shared" si="0"/>
@@ -13771,7 +13773,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U32" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
@@ -13788,16 +13790,16 @@
         <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P33" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="Q33" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R33" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S33" t="str">
         <f t="shared" si="0"/>
@@ -13808,7 +13810,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U33" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
@@ -13825,16 +13827,16 @@
         <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P34" t="s">
+        <v>898</v>
+      </c>
+      <c r="Q34" t="s">
         <v>899</v>
       </c>
-      <c r="Q34" t="s">
-        <v>900</v>
-      </c>
       <c r="R34" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S34" t="str">
         <f t="shared" si="0"/>
@@ -13845,7 +13847,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
@@ -13865,13 +13867,13 @@
         <v>659</v>
       </c>
       <c r="P35" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="Q35" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="R35" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S35" t="str">
         <f t="shared" si="0"/>
@@ -13882,7 +13884,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U35" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
@@ -13902,13 +13904,13 @@
         <v>659</v>
       </c>
       <c r="P36" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q36" t="s">
         <v>904</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>905</v>
-      </c>
-      <c r="R36" t="s">
-        <v>906</v>
       </c>
       <c r="S36" t="str">
         <f t="shared" si="0"/>
@@ -13919,7 +13921,7 @@
         <v>-0390-12-31</v>
       </c>
       <c r="U36" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
@@ -13939,13 +13941,13 @@
         <v>703</v>
       </c>
       <c r="P37" t="s">
+        <v>907</v>
+      </c>
+      <c r="Q37" t="s">
         <v>908</v>
       </c>
-      <c r="Q37" t="s">
-        <v>909</v>
-      </c>
       <c r="R37" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S37" t="str">
         <f t="shared" si="0"/>
@@ -13956,7 +13958,7 @@
         <v>-0390-12-31</v>
       </c>
       <c r="U37" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
@@ -13976,13 +13978,13 @@
         <v>703</v>
       </c>
       <c r="P38" t="s">
+        <v>910</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>899</v>
+      </c>
+      <c r="R38" t="s">
         <v>911</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>900</v>
-      </c>
-      <c r="R38" t="s">
-        <v>912</v>
       </c>
       <c r="S38" t="str">
         <f t="shared" si="0"/>
@@ -13993,7 +13995,7 @@
         <v>-0250-12-31</v>
       </c>
       <c r="U38" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
@@ -14013,13 +14015,13 @@
         <v>703</v>
       </c>
       <c r="P39" t="s">
+        <v>913</v>
+      </c>
+      <c r="Q39" t="s">
         <v>914</v>
       </c>
-      <c r="Q39" t="s">
-        <v>915</v>
-      </c>
       <c r="R39" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S39" t="str">
         <f t="shared" si="0"/>
@@ -14030,7 +14032,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U39" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
@@ -14047,16 +14049,16 @@
         <v>44</v>
       </c>
       <c r="J40" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P40" t="s">
+        <v>916</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>867</v>
+      </c>
+      <c r="R40" t="s">
         <v>917</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>868</v>
-      </c>
-      <c r="R40" t="s">
-        <v>918</v>
       </c>
       <c r="S40" t="str">
         <f t="shared" si="0"/>
@@ -14067,7 +14069,7 @@
         <v>-0100-12-31</v>
       </c>
       <c r="U40" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
@@ -14084,16 +14086,16 @@
         <v>410</v>
       </c>
       <c r="J41" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="P41" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q41" t="s">
         <v>920</v>
       </c>
-      <c r="Q41" t="s">
-        <v>921</v>
-      </c>
       <c r="R41" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S41" t="str">
         <f t="shared" si="0"/>
@@ -14104,7 +14106,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U41" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
@@ -14121,16 +14123,16 @@
         <v>48</v>
       </c>
       <c r="J42" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="P42" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q42" t="s">
         <v>923</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>924</v>
-      </c>
-      <c r="R42" t="s">
-        <v>925</v>
       </c>
       <c r="S42" t="str">
         <f t="shared" si="0"/>
@@ -14141,7 +14143,7 @@
         <v>-0200-12-31</v>
       </c>
       <c r="U42" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
@@ -14158,16 +14160,16 @@
         <v>51</v>
       </c>
       <c r="J43" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="P43" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="Q43" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="R43" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="S43" t="str">
         <f t="shared" si="0"/>
@@ -14178,7 +14180,7 @@
         <v>-0200-12-31</v>
       </c>
       <c r="U43" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.2">
@@ -14195,16 +14197,16 @@
         <v>54</v>
       </c>
       <c r="J44" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="P44" t="s">
+        <v>928</v>
+      </c>
+      <c r="Q44" t="s">
         <v>929</v>
       </c>
-      <c r="Q44" t="s">
-        <v>930</v>
-      </c>
       <c r="R44" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S44" t="str">
         <f t="shared" si="0"/>
@@ -14215,7 +14217,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U44" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
@@ -14226,7 +14228,7 @@
         <v>382</v>
       </c>
       <c r="G45" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I45" t="s">
         <v>57</v>
@@ -14235,13 +14237,13 @@
         <v>680</v>
       </c>
       <c r="P45" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q45" t="s">
         <v>932</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>933</v>
-      </c>
-      <c r="R45" t="s">
-        <v>934</v>
       </c>
       <c r="S45" t="str">
         <f t="shared" si="0"/>
@@ -14252,7 +14254,7 @@
         <v>-0550-12-31</v>
       </c>
       <c r="U45" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.2">
@@ -14272,13 +14274,13 @@
         <v>680</v>
       </c>
       <c r="P46" t="s">
+        <v>935</v>
+      </c>
+      <c r="Q46" t="s">
         <v>936</v>
       </c>
-      <c r="Q46" t="s">
-        <v>937</v>
-      </c>
       <c r="R46" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S46" t="str">
         <f t="shared" si="0"/>
@@ -14289,7 +14291,7 @@
         <v>-0520-12-31</v>
       </c>
       <c r="U46" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
@@ -14309,13 +14311,13 @@
         <v>658</v>
       </c>
       <c r="P47" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q47" t="s">
         <v>939</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>940</v>
-      </c>
-      <c r="R47" t="s">
-        <v>941</v>
       </c>
       <c r="S47" t="str">
         <f t="shared" si="0"/>
@@ -14326,7 +14328,7 @@
         <v>-0530-12-31</v>
       </c>
       <c r="U47" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
@@ -14346,13 +14348,13 @@
         <v>659</v>
       </c>
       <c r="P48" t="s">
+        <v>942</v>
+      </c>
+      <c r="Q48" t="s">
         <v>943</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>944</v>
-      </c>
-      <c r="R48" t="s">
-        <v>945</v>
       </c>
       <c r="S48" t="str">
         <f t="shared" si="0"/>
@@ -14363,7 +14365,7 @@
         <v>-0164-12-31</v>
       </c>
       <c r="U48" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
@@ -14383,13 +14385,13 @@
         <v>659</v>
       </c>
       <c r="P49" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q49" t="s">
         <v>947</v>
       </c>
-      <c r="Q49" t="s">
-        <v>948</v>
-      </c>
       <c r="R49" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S49" t="str">
         <f t="shared" si="0"/>
@@ -14400,7 +14402,7 @@
         <v>-0500-12-31</v>
       </c>
       <c r="U49" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
@@ -14420,13 +14422,13 @@
         <v>660</v>
       </c>
       <c r="P50" t="s">
+        <v>949</v>
+      </c>
+      <c r="Q50" t="s">
         <v>950</v>
       </c>
-      <c r="Q50" t="s">
-        <v>951</v>
-      </c>
       <c r="R50" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S50" t="str">
         <f t="shared" si="0"/>
@@ -14437,7 +14439,7 @@
         <v>-0300-12-31</v>
       </c>
       <c r="U50" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
@@ -14457,13 +14459,13 @@
         <v>661</v>
       </c>
       <c r="P51" t="s">
+        <v>952</v>
+      </c>
+      <c r="Q51" t="s">
         <v>953</v>
       </c>
-      <c r="Q51" t="s">
-        <v>954</v>
-      </c>
       <c r="R51" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S51" t="str">
         <f t="shared" si="0"/>
@@ -14474,7 +14476,7 @@
         <v>-0500-12-31</v>
       </c>
       <c r="U51" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
@@ -14491,16 +14493,16 @@
         <v>78</v>
       </c>
       <c r="J52" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="P52" t="s">
+        <v>955</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>936</v>
+      </c>
+      <c r="R52" t="s">
         <v>956</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>937</v>
-      </c>
-      <c r="R52" t="s">
-        <v>957</v>
       </c>
       <c r="S52" t="str">
         <f t="shared" si="0"/>
@@ -14511,7 +14513,7 @@
         <v>-0450-12-31</v>
       </c>
       <c r="U52" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
@@ -14528,16 +14530,16 @@
         <v>80</v>
       </c>
       <c r="J53" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P53" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Q53" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="R53" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="S53" t="str">
         <f t="shared" si="0"/>
@@ -14548,7 +14550,7 @@
         <v>-0250-12-31</v>
       </c>
       <c r="U53" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
@@ -14565,16 +14567,16 @@
         <v>82</v>
       </c>
       <c r="J54" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="P54" t="s">
+        <v>960</v>
+      </c>
+      <c r="Q54" t="s">
         <v>961</v>
       </c>
-      <c r="Q54" t="s">
-        <v>962</v>
-      </c>
       <c r="R54" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S54" t="str">
         <f t="shared" si="0"/>
@@ -14585,7 +14587,7 @@
         <v>-0500-12-31</v>
       </c>
       <c r="U54" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
@@ -14602,16 +14604,16 @@
         <v>85</v>
       </c>
       <c r="J55" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="P55" t="s">
+        <v>963</v>
+      </c>
+      <c r="Q55" t="s">
         <v>964</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="R55" t="s">
         <v>965</v>
-      </c>
-      <c r="R55" t="s">
-        <v>966</v>
       </c>
       <c r="S55" t="str">
         <f t="shared" si="0"/>
@@ -14622,7 +14624,7 @@
         <v>-0612-12-31</v>
       </c>
       <c r="U55" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
@@ -14639,16 +14641,16 @@
         <v>87</v>
       </c>
       <c r="J56" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="P56" t="s">
+        <v>967</v>
+      </c>
+      <c r="Q56" t="s">
         <v>968</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>969</v>
-      </c>
-      <c r="R56" t="s">
-        <v>970</v>
       </c>
       <c r="S56" t="str">
         <f t="shared" si="0"/>
@@ -14659,7 +14661,7 @@
         <v>-0587-12-31</v>
       </c>
       <c r="U56" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
@@ -14676,16 +14678,16 @@
         <v>90</v>
       </c>
       <c r="J57" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="P57" t="s">
+        <v>971</v>
+      </c>
+      <c r="Q57" t="s">
         <v>972</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="R57" t="s">
         <v>973</v>
-      </c>
-      <c r="R57" t="s">
-        <v>974</v>
       </c>
       <c r="S57" t="str">
         <f t="shared" si="0"/>
@@ -14696,7 +14698,7 @@
         <v>-0625-12-31</v>
       </c>
       <c r="U57" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
@@ -14713,16 +14715,16 @@
         <v>93</v>
       </c>
       <c r="J58" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="P58" t="s">
+        <v>975</v>
+      </c>
+      <c r="Q58" t="s">
         <v>976</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>977</v>
-      </c>
-      <c r="R58" t="s">
-        <v>978</v>
       </c>
       <c r="S58" t="str">
         <f t="shared" si="0"/>
@@ -14733,7 +14735,7 @@
         <v>-0519-12-31</v>
       </c>
       <c r="U58" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
@@ -14750,16 +14752,16 @@
         <v>96</v>
       </c>
       <c r="J59" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="P59" t="s">
+        <v>979</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>976</v>
+      </c>
+      <c r="R59" t="s">
         <v>980</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>977</v>
-      </c>
-      <c r="R59" t="s">
-        <v>981</v>
       </c>
       <c r="S59" t="str">
         <f t="shared" si="0"/>
@@ -14770,7 +14772,7 @@
         <v>-0440-12-31</v>
       </c>
       <c r="U59" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
@@ -14787,16 +14789,16 @@
         <v>99</v>
       </c>
       <c r="J60" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="P60" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="Q60" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="R60" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="S60" t="str">
         <f t="shared" si="0"/>
@@ -14807,7 +14809,7 @@
         <v>-0400-12-31</v>
       </c>
       <c r="U60" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
@@ -14824,16 +14826,16 @@
         <v>102</v>
       </c>
       <c r="J61" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="P61" t="s">
+        <v>984</v>
+      </c>
+      <c r="Q61" t="s">
         <v>985</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
         <v>986</v>
-      </c>
-      <c r="R61" t="s">
-        <v>987</v>
       </c>
       <c r="S61" t="str">
         <f t="shared" si="0"/>
@@ -14844,7 +14846,7 @@
         <v>0100-12-31</v>
       </c>
       <c r="U61" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
@@ -14855,22 +14857,22 @@
         <v>283</v>
       </c>
       <c r="G62" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I62" t="s">
         <v>105</v>
       </c>
       <c r="J62" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="P62" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q62" t="s">
         <v>989</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>990</v>
-      </c>
-      <c r="R62" t="s">
-        <v>991</v>
       </c>
       <c r="S62" t="str">
         <f t="shared" si="0"/>
@@ -14881,7 +14883,7 @@
         <v>0075-12-31</v>
       </c>
       <c r="U62" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
@@ -14892,22 +14894,22 @@
         <v>391</v>
       </c>
       <c r="G63" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I63" t="s">
         <v>108</v>
       </c>
       <c r="J63" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P63" t="s">
+        <v>992</v>
+      </c>
+      <c r="Q63" t="s">
         <v>993</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="R63" t="s">
         <v>994</v>
-      </c>
-      <c r="R63" t="s">
-        <v>995</v>
       </c>
       <c r="S63" t="str">
         <f t="shared" si="0"/>
@@ -14918,7 +14920,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U63" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
@@ -14929,22 +14931,22 @@
         <v>392</v>
       </c>
       <c r="G64" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I64" t="s">
         <v>111</v>
       </c>
       <c r="J64" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="P64" t="s">
+        <v>996</v>
+      </c>
+      <c r="Q64" t="s">
         <v>997</v>
       </c>
-      <c r="Q64" t="s">
-        <v>998</v>
-      </c>
       <c r="R64" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S64" t="str">
         <f t="shared" si="0"/>
@@ -14955,7 +14957,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U64" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.2">
@@ -14966,22 +14968,22 @@
         <v>393</v>
       </c>
       <c r="G65" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I65" t="s">
         <v>113</v>
       </c>
       <c r="J65" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="P65" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Q65" t="s">
+        <v>993</v>
+      </c>
+      <c r="R65" t="s">
         <v>994</v>
-      </c>
-      <c r="R65" t="s">
-        <v>995</v>
       </c>
       <c r="S65" t="str">
         <f t="shared" si="0"/>
@@ -14992,7 +14994,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U65" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.2">
@@ -15009,16 +15011,16 @@
         <v>115</v>
       </c>
       <c r="J66" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="P66" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q66" t="s">
         <v>1002</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>1003</v>
-      </c>
-      <c r="R66" t="s">
-        <v>1004</v>
       </c>
       <c r="S66" t="str">
         <f t="shared" si="0"/>
@@ -15029,7 +15031,7 @@
         <v>0058-12-31</v>
       </c>
       <c r="U66" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.2">
@@ -15049,13 +15051,13 @@
         <v>706</v>
       </c>
       <c r="P67" t="s">
+        <v>1005</v>
+      </c>
+      <c r="Q67" t="s">
         <v>1006</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
         <v>1007</v>
-      </c>
-      <c r="R67" t="s">
-        <v>1008</v>
       </c>
       <c r="S67" t="str">
         <f t="shared" si="0"/>
@@ -15066,7 +15068,7 @@
         <v>0055-12-31</v>
       </c>
       <c r="U67" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.2">
@@ -15083,16 +15085,16 @@
         <v>119</v>
       </c>
       <c r="J68" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="P68" t="s">
+        <v>1009</v>
+      </c>
+      <c r="Q68" t="s">
         <v>1010</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>1011</v>
-      </c>
-      <c r="R68" t="s">
-        <v>1012</v>
       </c>
       <c r="S68" t="str">
         <f t="shared" si="0"/>
@@ -15103,7 +15105,7 @@
         <v>0057-12-31</v>
       </c>
       <c r="U68" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
@@ -15114,7 +15116,7 @@
         <v>396</v>
       </c>
       <c r="G69" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I69" t="s">
         <v>122</v>
@@ -15123,13 +15125,13 @@
         <v>663</v>
       </c>
       <c r="P69" t="s">
+        <v>1013</v>
+      </c>
+      <c r="Q69" t="s">
         <v>1014</v>
       </c>
-      <c r="Q69" t="s">
-        <v>1015</v>
-      </c>
       <c r="R69" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="S69" t="str">
         <f t="shared" si="0"/>
@@ -15140,7 +15142,7 @@
         <v>0055-12-31</v>
       </c>
       <c r="U69" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.2">
@@ -15160,13 +15162,13 @@
         <v>663</v>
       </c>
       <c r="P70" t="s">
+        <v>1016</v>
+      </c>
+      <c r="Q70" t="s">
         <v>1017</v>
       </c>
-      <c r="Q70" t="s">
-        <v>1018</v>
-      </c>
       <c r="R70" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="S70" t="str">
         <f t="shared" si="0"/>
@@ -15177,7 +15179,7 @@
         <v>0100-12-31</v>
       </c>
       <c r="U70" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">
@@ -15188,7 +15190,7 @@
         <v>397</v>
       </c>
       <c r="G71" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I71" t="s">
         <v>128</v>
@@ -15197,13 +15199,13 @@
         <v>663</v>
       </c>
       <c r="P71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="Q71" t="s">
         <v>1020</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>1021</v>
-      </c>
-      <c r="R71" t="s">
-        <v>1022</v>
       </c>
       <c r="S71" t="str">
         <f t="shared" si="0"/>
@@ -15214,7 +15216,7 @@
         <v>0062-12-31</v>
       </c>
       <c r="U71" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.2">
@@ -15234,13 +15236,13 @@
         <v>663</v>
       </c>
       <c r="P72" t="s">
+        <v>1023</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>1017</v>
+      </c>
+      <c r="R72" t="s">
         <v>1024</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>1018</v>
-      </c>
-      <c r="R72" t="s">
-        <v>1025</v>
       </c>
       <c r="S72" t="str">
         <f t="shared" si="0"/>
@@ -15251,7 +15253,7 @@
         <v>0090-12-31</v>
       </c>
       <c r="U72" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.2">
@@ -15271,13 +15273,13 @@
         <v>663</v>
       </c>
       <c r="P73" t="s">
+        <v>1026</v>
+      </c>
+      <c r="Q73" t="s">
         <v>1027</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R73" t="s">
         <v>1028</v>
-      </c>
-      <c r="R73" t="s">
-        <v>1029</v>
       </c>
       <c r="S73" t="str">
         <f t="shared" si="0"/>
@@ -15288,7 +15290,7 @@
         <v>0051-12-31</v>
       </c>
       <c r="U73" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.2">
@@ -15299,7 +15301,7 @@
         <v>308</v>
       </c>
       <c r="G74" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I74" t="s">
         <v>137</v>
@@ -15308,13 +15310,13 @@
         <v>663</v>
       </c>
       <c r="P74" t="s">
+        <v>1030</v>
+      </c>
+      <c r="Q74" t="s">
         <v>1031</v>
       </c>
-      <c r="Q74" t="s">
-        <v>1032</v>
-      </c>
       <c r="R74" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="S74" t="str">
         <f t="shared" si="0"/>
@@ -15325,7 +15327,7 @@
         <v>0100-12-31</v>
       </c>
       <c r="U74" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.2">
@@ -15336,7 +15338,7 @@
         <v>310</v>
       </c>
       <c r="G75" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I75" t="s">
         <v>140</v>
@@ -15345,13 +15347,13 @@
         <v>663</v>
       </c>
       <c r="P75" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q75" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="R75" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S75" t="str">
         <f t="shared" si="0"/>
@@ -15362,7 +15364,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U75" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.2">
@@ -15382,13 +15384,13 @@
         <v>663</v>
       </c>
       <c r="P76" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q76" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="R76" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S76" t="str">
         <f t="shared" si="0"/>
@@ -15399,7 +15401,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U76" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.2">
@@ -15419,13 +15421,13 @@
         <v>663</v>
       </c>
       <c r="P77" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q77" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="R77" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S77" t="str">
         <f t="shared" si="0"/>
@@ -15436,7 +15438,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U77" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.2">
@@ -15456,13 +15458,13 @@
         <v>663</v>
       </c>
       <c r="P78" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="Q78" t="s">
+        <v>1020</v>
+      </c>
+      <c r="R78" t="s">
         <v>1021</v>
-      </c>
-      <c r="R78" t="s">
-        <v>1022</v>
       </c>
       <c r="S78" t="str">
         <f t="shared" si="0"/>
@@ -15473,7 +15475,7 @@
         <v>0062-12-31</v>
       </c>
       <c r="U78" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.2">
@@ -15493,13 +15495,13 @@
         <v>663</v>
       </c>
       <c r="P79" t="s">
+        <v>1040</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>1017</v>
+      </c>
+      <c r="R79" t="s">
         <v>1041</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>1018</v>
-      </c>
-      <c r="R79" t="s">
-        <v>1042</v>
       </c>
       <c r="S79" t="str">
         <f t="shared" si="0"/>
@@ -15510,7 +15512,7 @@
         <v>0095-12-31</v>
       </c>
       <c r="U79" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.2">
@@ -15530,13 +15532,13 @@
         <v>663</v>
       </c>
       <c r="P80" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q80" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R80" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S80" t="str">
         <f t="shared" si="0"/>
@@ -15547,7 +15549,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U80" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.2">
@@ -15567,13 +15569,13 @@
         <v>663</v>
       </c>
       <c r="P81" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q81" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="R81" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="S81" t="str">
         <f t="shared" si="0"/>
@@ -15584,7 +15586,7 @@
         <v>0090-12-31</v>
       </c>
       <c r="U81" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
@@ -15604,13 +15606,13 @@
         <v>677</v>
       </c>
       <c r="P82" t="s">
+        <v>1047</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>993</v>
+      </c>
+      <c r="R82" t="s">
         <v>1048</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>994</v>
-      </c>
-      <c r="R82" t="s">
-        <v>1049</v>
       </c>
       <c r="S82" t="str">
         <f t="shared" si="0"/>
@@ -15621,7 +15623,7 @@
         <v>0150-12-31</v>
       </c>
       <c r="U82" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
@@ -15641,13 +15643,13 @@
         <v>667</v>
       </c>
       <c r="P83" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q83" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="R83" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S83" t="str">
         <f t="shared" si="0"/>
@@ -15658,7 +15660,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U83" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
@@ -15678,13 +15680,13 @@
         <v>668</v>
       </c>
       <c r="P84" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="Q84" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="R84" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S84" t="str">
         <f t="shared" si="0"/>
@@ -15695,7 +15697,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U84" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
@@ -15715,13 +15717,13 @@
         <v>668</v>
       </c>
       <c r="P85" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q85" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="R85" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S85" t="str">
         <f t="shared" si="0"/>
@@ -15732,7 +15734,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U85" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
@@ -15752,13 +15754,13 @@
         <v>706</v>
       </c>
       <c r="P86" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q86" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="R86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S86" t="str">
         <f t="shared" si="0"/>
@@ -15769,7 +15771,7 @@
         <v>0110-12-31</v>
       </c>
       <c r="U86" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
@@ -15789,13 +15791,13 @@
         <v>706</v>
       </c>
       <c r="P87" t="s">
+        <v>1057</v>
+      </c>
+      <c r="Q87" t="s">
         <v>1058</v>
       </c>
-      <c r="Q87" t="s">
+      <c r="R87" t="s">
         <v>1059</v>
-      </c>
-      <c r="R87" t="s">
-        <v>1060</v>
       </c>
       <c r="S87" t="str">
         <f t="shared" ref="S87:T87" si="2">SUBSTITUTE(Q87," ", "")</f>
@@ -15806,7 +15808,7 @@
         <v>0096-12-31</v>
       </c>
       <c r="U87" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
@@ -15828,7 +15830,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F89" t="s">
         <v>400</v>
@@ -15848,7 +15850,7 @@
         <v>329</v>
       </c>
       <c r="G90" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I90" t="s">
         <v>183</v>
@@ -15870,7 +15872,7 @@
         <v>333</v>
       </c>
       <c r="G92" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
@@ -15878,7 +15880,7 @@
         <v>336</v>
       </c>
       <c r="G93" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
@@ -15886,16 +15888,16 @@
         <v>339</v>
       </c>
       <c r="G94" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P94" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="Q94" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="Q94" s="1" t="s">
+      <c r="R94" s="1" t="s">
         <v>1212</v>
-      </c>
-      <c r="R94" s="1" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
@@ -15903,16 +15905,16 @@
         <v>341</v>
       </c>
       <c r="G95" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P95" t="s">
         <v>439</v>
       </c>
       <c r="Q95" t="s">
+        <v>1213</v>
+      </c>
+      <c r="R95" t="s">
         <v>1214</v>
-      </c>
-      <c r="R95" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
@@ -15920,16 +15922,16 @@
         <v>343</v>
       </c>
       <c r="G96" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P96" t="s">
         <v>444</v>
       </c>
       <c r="Q96" t="s">
+        <v>1215</v>
+      </c>
+      <c r="R96" t="s">
         <v>1216</v>
-      </c>
-      <c r="R96" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="97" spans="6:18" x14ac:dyDescent="0.2">
@@ -15937,16 +15939,16 @@
         <v>345</v>
       </c>
       <c r="G97" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P97" t="s">
         <v>446</v>
       </c>
       <c r="Q97" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="R97" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="98" spans="6:18" x14ac:dyDescent="0.2">
@@ -15954,16 +15956,16 @@
         <v>347</v>
       </c>
       <c r="G98" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P98" t="s">
         <v>577</v>
       </c>
       <c r="Q98" t="s">
+        <v>1218</v>
+      </c>
+      <c r="R98" t="s">
         <v>1219</v>
-      </c>
-      <c r="R98" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="99" spans="6:18" x14ac:dyDescent="0.2">
@@ -15971,16 +15973,16 @@
         <v>349</v>
       </c>
       <c r="G99" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P99" t="s">
         <v>578</v>
       </c>
       <c r="Q99" t="s">
+        <v>1220</v>
+      </c>
+      <c r="R99" t="s">
         <v>1221</v>
-      </c>
-      <c r="R99" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="100" spans="6:18" x14ac:dyDescent="0.2">
@@ -15988,7 +15990,7 @@
         <v>351</v>
       </c>
       <c r="G100" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="101" spans="6:18" x14ac:dyDescent="0.2">
@@ -16004,7 +16006,7 @@
         <v>355</v>
       </c>
       <c r="G102" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="103" spans="6:18" x14ac:dyDescent="0.2">
@@ -16028,7 +16030,7 @@
         <v>411</v>
       </c>
       <c r="G105" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="106" spans="6:18" x14ac:dyDescent="0.2">
@@ -16036,7 +16038,7 @@
         <v>364</v>
       </c>
       <c r="G106" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="107" spans="6:18" x14ac:dyDescent="0.2">
@@ -16044,7 +16046,7 @@
         <v>366</v>
       </c>
       <c r="G107" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="108" spans="6:18" x14ac:dyDescent="0.2">
@@ -16052,7 +16054,7 @@
         <v>368</v>
       </c>
       <c r="G108" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="109" spans="6:18" x14ac:dyDescent="0.2">
@@ -16068,7 +16070,7 @@
         <v>402</v>
       </c>
       <c r="G110" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="111" spans="6:18" x14ac:dyDescent="0.2">
@@ -16076,7 +16078,7 @@
         <v>403</v>
       </c>
       <c r="G111" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="112" spans="6:18" x14ac:dyDescent="0.2">
@@ -16092,7 +16094,7 @@
         <v>405</v>
       </c>
       <c r="G113" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.2">
@@ -16100,7 +16102,7 @@
         <v>376</v>
       </c>
       <c r="G114" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>

--- a/data/research/research.xlsx
+++ b/data/research/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksnyder/Sites/public-domain-books/data/research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8119A8E3-5CF4-5240-83D8-E5D3A8A9D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBD09E7-1716-C942-8649-B71886874926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53100" yWindow="700" windowWidth="47220" windowHeight="25960" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19420" activeTab="2" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Scratch" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Books!$A$1:$E$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Books!$A$1:$E$180</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="1293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1303">
   <si>
     <t>Gen</t>
   </si>
@@ -3922,6 +3922,36 @@
   </si>
   <si>
     <t>["Testament of Zebulun","The Testament of Zebulun"]</t>
+  </si>
+  <si>
+    <t>Jasher</t>
+  </si>
+  <si>
+    <t>["Sepir Ha Yasher","Sefer haYashar","The Book of Jasher","Book of Jasher"]</t>
+  </si>
+  <si>
+    <t>1200-01-01</t>
+  </si>
+  <si>
+    <t>1300-01-01</t>
+  </si>
+  <si>
+    <t>Ascension of Isaiah</t>
+  </si>
+  <si>
+    <t>["Apocrypha"]</t>
+  </si>
+  <si>
+    <t>["The Ascension of Isaiah"]</t>
+  </si>
+  <si>
+    <t>0200-01-01</t>
+  </si>
+  <si>
+    <t>AscIsa</t>
+  </si>
+  <si>
+    <t>Translated by R. H. Charles</t>
   </si>
 </sst>
 </file>
@@ -4025,7 +4055,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4048,6 +4078,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4383,13 +4414,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2457BBF2-065A-6B4B-8450-DD145766C676}">
-  <dimension ref="A1:O208"/>
+  <dimension ref="A1:O210"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="128.83203125" customWidth="1"/>
+    <col min="5" max="5" width="43" customWidth="1"/>
     <col min="6" max="6" width="46.5" customWidth="1"/>
     <col min="7" max="8" width="10.33203125" style="7" customWidth="1"/>
     <col min="9" max="9" width="29.33203125" style="7" customWidth="1"/>
@@ -10571,7 +10602,7 @@
         <v>false</v>
       </c>
       <c r="O130" s="3" t="str">
-        <f t="shared" ref="O130:O178" si="11">"{ ""workOsisID"": """&amp;G130&amp;""", ""bookName"": """&amp;A130&amp;""", ""bookSubtitle"": """&amp;B130&amp;""", ""bookOsisID"": """&amp;C130&amp;""", ""paratext"": "&amp;IF(D130="","null",""""&amp;D130&amp;"""")&amp;", ""groups"": "&amp;E130&amp;", ""aliases"": "&amp;F130&amp;", ""chapterLabel"": """&amp;L130&amp;""", ""verseLabel"": """&amp;M130&amp;""", ""authors"": "&amp;H130&amp;", ""dateEarliest"": """&amp;J130&amp;""", ""dateLatest"": """&amp;K130&amp;""", ""hasData"": "&amp;N130&amp;", ""traditions"": "&amp;I130&amp;" },"</f>
+        <f t="shared" ref="O130:O180" si="11">"{ ""workOsisID"": """&amp;G130&amp;""", ""bookName"": """&amp;A130&amp;""", ""bookSubtitle"": """&amp;B130&amp;""", ""bookOsisID"": """&amp;C130&amp;""", ""paratext"": "&amp;IF(D130="","null",""""&amp;D130&amp;"""")&amp;", ""groups"": "&amp;E130&amp;", ""aliases"": "&amp;F130&amp;", ""chapterLabel"": """&amp;L130&amp;""", ""verseLabel"": """&amp;M130&amp;""", ""authors"": "&amp;H130&amp;", ""dateEarliest"": """&amp;J130&amp;""", ""dateLatest"": """&amp;K130&amp;""", ""hasData"": "&amp;N130&amp;", ""traditions"": "&amp;I130&amp;" },"</f>
         <v>{ "workOsisID": "", "bookName": "2 Baruch", "bookSubtitle": "", "bookOsisID": "2Bar", "paratext": "2BA", "groups": ["Syriac Orthodox Canon", "Apocrypha"], "aliases": ["(Syriac) Apocalypse of Baruch"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Baruch"], "dateEarliest": "0080-01-01", "dateLatest": "0100-12-31", "hasData": false, "traditions": ["academic"] },</v>
       </c>
     </row>
@@ -10693,7 +10724,7 @@
         <v>471</v>
       </c>
       <c r="N133" t="str">
-        <f t="shared" ref="N133:N157" si="12">"false"</f>
+        <f t="shared" ref="N133:N159" si="12">"false"</f>
         <v>false</v>
       </c>
       <c r="O133" s="3" t="str">
@@ -11728,7 +11759,7 @@
         <v>375</v>
       </c>
       <c r="E156" t="s">
-        <v>457</v>
+        <v>1298</v>
       </c>
       <c r="F156" t="s">
         <v>441</v>
@@ -11760,214 +11791,209 @@
       </c>
       <c r="O156" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "Academic", "bookName": "Diatessaron", "bookSubtitle": "", "bookOsisID": "TatDiat", "paratext": null, "groups": ["Apocrypha", "Apocrypha"], "aliases": ["Tatian's Diatessaron","Tatian"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Tatian"], "dateEarliest": "0160-01-01", "dateLatest": "0175-12-31", "hasData": false, "traditions": ["academic"] },</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+        <v>{ "workOsisID": "Academic", "bookName": "Diatessaron", "bookSubtitle": "", "bookOsisID": "TatDiat", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Tatian's Diatessaron","Tatian"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Tatian"], "dateEarliest": "0160-01-01", "dateLatest": "0175-12-31", "hasData": false, "traditions": ["academic"] },</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="J157" s="16" t="s">
+        <v>1295</v>
+      </c>
+      <c r="K157" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="M157" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N157" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O157" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>{ "workOsisID": "Academic", "bookName": "Jasher", "bookSubtitle": "", "bookOsisID": "Jasher", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Sepir Ha Yasher","Sefer haYashar","The Book of Jasher","Book of Jasher"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Moses"], "dateEarliest": "1200-01-01", "dateLatest": "1300-01-01", "hasData": true, "traditions": ["academic"] },</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F158" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="J158" s="16" t="s">
+        <v>1130</v>
+      </c>
+      <c r="K158" s="16" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N158" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O158" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>{ "workOsisID": "Academic", "bookName": "Ascension of Isaiah", "bookSubtitle": "", "bookOsisID": "AscIsa", "paratext": null, "groups": ["Apocrypha"], "aliases": ["The Ascension of Isaiah"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Isaiah"], "dateEarliest": "0150-01-01", "dateLatest": "0200-01-01", "hasData": true, "traditions": ["academic"] },</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>406</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C159" t="s">
         <v>377</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D159" t="s">
         <v>378</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E159" t="s">
         <v>457</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F159" t="s">
         <v>669</v>
       </c>
-      <c r="G157" s="7" t="s">
+      <c r="G159" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="H157" s="7" t="s">
+      <c r="H159" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="I157" s="7" t="s">
+      <c r="I159" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="J157" s="14" t="s">
+      <c r="J159" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K157" s="14" t="s">
+      <c r="K159" s="14" t="s">
         <v>1132</v>
       </c>
-      <c r="L157" t="s">
-        <v>468</v>
-      </c>
-      <c r="M157" t="s">
-        <v>471</v>
-      </c>
-      <c r="N157" t="str">
+      <c r="L159" t="s">
+        <v>468</v>
+      </c>
+      <c r="M159" t="s">
+        <v>471</v>
+      </c>
+      <c r="N159" t="str">
         <f t="shared" si="12"/>
         <v>false</v>
       </c>
-      <c r="O157" s="3" t="str">
+      <c r="O159" s="3" t="str">
         <f t="shared" si="11"/>
         <v>{ "workOsisID": "Academic", "bookName": "Metrical Psalms", "bookSubtitle": "", "bookOsisID": "PsMet", "paratext": "PSB", "groups": ["Apocrypha", "Apocrypha"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": [], "dateEarliest": "0160-01-01", "dateLatest": "0180-12-31", "hasData": false, "traditions": ["academic"] },</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
+    <row r="160" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C160" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="E160" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F160" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="G158" s="6" t="s">
+      <c r="G160" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="H158" s="6" t="s">
+      <c r="H160" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="I158" s="6" t="s">
+      <c r="I160" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="J158" s="15" t="s">
+      <c r="J160" s="15" t="s">
         <v>583</v>
       </c>
-      <c r="K158" s="15" t="s">
+      <c r="K160" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="L158" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M158" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="N158" s="3" t="str">
-        <f t="shared" ref="N158:N178" si="14">"true"</f>
+      <c r="L160" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="M160" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N160" s="3" t="str">
+        <f t="shared" ref="N160:N180" si="14">"true"</f>
         <v>true</v>
       </c>
-      <c r="O158" s="3" t="str">
+      <c r="O160" s="3" t="str">
         <f t="shared" si="11"/>
         <v>{ "workOsisID": "BofM", "bookName": "1 Nephi", "bookSubtitle": "", "bookOsisID": "1Ne", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": ["1 Ne", "1st Nephi", "First Nephi", "The First Book of Nephi","I Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Nephi"], "dateEarliest": "-0600-01-01", "dateLatest": "-0570-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="I159" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="J159" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="K159" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="L159" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M159" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="N159" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>true</v>
-      </c>
-      <c r="O159" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "2 Nephi", "bookSubtitle": "", "bookOsisID": "2Ne", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": ["2 Ne", "2nd Nephi", "Second Nephi", "The Second Book of Nephi", "II Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Nephi"], "dateEarliest": "-0588-01-01", "dateLatest": "-0545-01-01", "hasData": true, "traditions": ["lds"] },</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="I160" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="J160" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="K160" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M160" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="N160" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>true</v>
-      </c>
-      <c r="O160" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Jacob", "bookSubtitle": "the Brother of Nephi", "bookOsisID": "Jac", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jacob"], "dateEarliest": "-0544-01-01", "dateLatest": "-0421-01-01", "hasData": true, "traditions": ["lds"] },</v>
-      </c>
-    </row>
     <row r="161" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>458</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>478</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>692</v>
+        <v>663</v>
       </c>
       <c r="I161" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J161" s="15" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="K161" s="15" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L161" s="3" t="s">
         <v>468</v>
@@ -11981,15 +12007,18 @@
       </c>
       <c r="O161" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Enos", "bookSubtitle": "", "bookOsisID": "Enos", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Enos"], "dateEarliest": "-0420-01-01", "dateLatest": "-0420-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "2 Nephi", "bookSubtitle": "", "bookOsisID": "2Ne", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": ["2 Ne", "2nd Nephi", "Second Nephi", "The Second Book of Nephi", "II Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Nephi"], "dateEarliest": "-0588-01-01", "dateLatest": "-0545-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="162" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>452</v>
+        <v>416</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>704</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>458</v>
@@ -12001,16 +12030,16 @@
         <v>478</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="I162" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J162" s="15" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="K162" s="15" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="L162" s="3" t="s">
         <v>468</v>
@@ -12024,15 +12053,15 @@
       </c>
       <c r="O162" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Jarom", "bookSubtitle": "", "bookOsisID": "Jar", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jarom"], "dateEarliest": "-0399-01-01", "dateLatest": "-0361-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Jacob", "bookSubtitle": "the Brother of Nephi", "bookOsisID": "Jac", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jacob"], "dateEarliest": "-0544-01-01", "dateLatest": "-0421-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="163" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>458</v>
@@ -12044,16 +12073,16 @@
         <v>478</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I163" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J163" s="15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K163" s="15" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="L163" s="3" t="s">
         <v>468</v>
@@ -12067,18 +12096,18 @@
       </c>
       <c r="O163" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Omni", "bookSubtitle": "", "bookOsisID": "Omni", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Omni","Chemish","Abinadom","Amaleki"], "dateEarliest": "-0323-01-01", "dateLatest": "-0130-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Enos", "bookSubtitle": "", "bookOsisID": "Enos", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Enos"], "dateEarliest": "-0420-01-01", "dateLatest": "-0420-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="164" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>669</v>
@@ -12087,16 +12116,16 @@
         <v>478</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="I164" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J164" s="15" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K164" s="15" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L164" s="3" t="s">
         <v>468</v>
@@ -12110,18 +12139,18 @@
       </c>
       <c r="O164" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Words of Mormon", "bookSubtitle": "", "bookOsisID": "WoM", "paratext": null, "groups": ["Book of Mormon", "LDS","Mormon"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0385-01-01", "dateLatest": "0385-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Jarom", "bookSubtitle": "", "bookOsisID": "Jar", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Jarom"], "dateEarliest": "-0399-01-01", "dateLatest": "-0361-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="165" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>669</v>
@@ -12130,16 +12159,16 @@
         <v>478</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>665</v>
+        <v>694</v>
       </c>
       <c r="I165" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J165" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="K165" s="15" t="s">
         <v>593</v>
-      </c>
-      <c r="K165" s="15" t="s">
-        <v>595</v>
       </c>
       <c r="L165" s="3" t="s">
         <v>468</v>
@@ -12153,21 +12182,18 @@
       </c>
       <c r="O165" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Mosiah", "bookSubtitle": "", "bookOsisID": "Mosi", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0130-01-01", "dateLatest": "-0091-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Omni", "bookSubtitle": "", "bookOsisID": "Omni", "paratext": null, "groups": ["Book of Mormon", "Small Plates of Nephi", "LDS"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Omni","Chemish","Abinadom","Amaleki"], "dateEarliest": "-0323-01-01", "dateLatest": "-0130-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="166" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>705</v>
+        <v>420</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>669</v>
@@ -12182,10 +12208,10 @@
         <v>744</v>
       </c>
       <c r="J166" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K166" s="15" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L166" s="3" t="s">
         <v>468</v>
@@ -12199,21 +12225,21 @@
       </c>
       <c r="O166" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Alma", "bookSubtitle": "the Son of Alma", "bookOsisID": "Alma", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0091-01-01", "dateLatest": "-0052-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Words of Mormon", "bookSubtitle": "", "bookOsisID": "WoM", "paratext": null, "groups": ["Book of Mormon", "LDS","Mormon"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0385-01-01", "dateLatest": "0385-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="167" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>463</v>
+        <v>669</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>478</v>
@@ -12225,10 +12251,10 @@
         <v>744</v>
       </c>
       <c r="J167" s="15" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="K167" s="15" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L167" s="3" t="s">
         <v>468</v>
@@ -12242,24 +12268,24 @@
       </c>
       <c r="O167" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Helaman", "bookSubtitle": "", "bookOsisID": "Hel", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["He", "Hlm", "Helm"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0052-01-01", "dateLatest": "-0001-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Mosiah", "bookSubtitle": "", "bookOsisID": "Mosi", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0130-01-01", "dateLatest": "-0091-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>1208</v>
+        <v>669</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>478</v>
@@ -12271,10 +12297,10 @@
         <v>744</v>
       </c>
       <c r="J168" s="15" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K168" s="15" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L168" s="3" t="s">
         <v>468</v>
@@ -12288,24 +12314,21 @@
       </c>
       <c r="O168" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "3 Nephi", "bookSubtitle": "the Son of Nephi, Who Was the Son of Helaman", "bookOsisID": "3Ne", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["3 Ne", "3rd Nephi", "Third Nephi","The Third Book of Nephi","III Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0005-01-01", "dateLatest": "0035-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Alma", "bookSubtitle": "the Son of Alma", "bookOsisID": "Alma", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0091-01-01", "dateLatest": "-0052-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="169" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>702</v>
+        <v>425</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>1209</v>
+        <v>463</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>478</v>
@@ -12317,10 +12340,10 @@
         <v>744</v>
       </c>
       <c r="J169" s="15" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K169" s="15" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="L169" s="3" t="s">
         <v>468</v>
@@ -12334,21 +12357,24 @@
       </c>
       <c r="O169" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "4 Nephi", "bookSubtitle": "Who Is the Son of Nephi—One of the Disciples of Jesus Christ", "bookOsisID": "4Ne", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["4 Ne", "4th Nephi", "Fourth Nephi","The Fourth Book of Nephi","IV Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0035-01-01", "dateLatest": "0321-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Helaman", "bookSubtitle": "", "bookOsisID": "Hel", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["He", "Hlm", "Helm"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-0052-01-01", "dateLatest": "-0001-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="170" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>703</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>719</v>
+        <v>1208</v>
       </c>
       <c r="G170" s="6" t="s">
         <v>478</v>
@@ -12360,10 +12386,10 @@
         <v>744</v>
       </c>
       <c r="J170" s="15" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="K170" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="L170" s="3" t="s">
         <v>468</v>
@@ -12377,24 +12403,24 @@
       </c>
       <c r="O170" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Mormon", "bookSubtitle": "", "bookOsisID": "Morm", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Mmn"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0321-01-01", "dateLatest": "0421-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "3 Nephi", "bookSubtitle": "the Son of Nephi, Who Was the Son of Helaman", "bookOsisID": "3Ne", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["3 Ne", "3rd Nephi", "Third Nephi","The Third Book of Nephi","III Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0005-01-01", "dateLatest": "0035-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="171" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G171" s="6" t="s">
         <v>478</v>
@@ -12406,10 +12432,10 @@
         <v>744</v>
       </c>
       <c r="J171" s="15" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K171" s="15" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L171" s="3" t="s">
         <v>468</v>
@@ -12423,21 +12449,21 @@
       </c>
       <c r="O171" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Ether", "bookSubtitle": "The record of the Jaredites, taken from the twenty-four plates found by the people of Limhi in the days of King Mosiah.", "bookOsisID": "Eth", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Ethr"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-2200-01-01", "dateLatest": "-0350-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "4 Nephi", "bookSubtitle": "Who Is the Son of Nephi—One of the Disciples of Jesus Christ", "bookOsisID": "4Ne", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["4 Ne", "4th Nephi", "Fourth Nephi","The Fourth Book of Nephi","IV Nephi"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0035-01-01", "dateLatest": "0321-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>460</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G172" s="6" t="s">
         <v>478</v>
@@ -12449,10 +12475,10 @@
         <v>744</v>
       </c>
       <c r="J172" s="15" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="K172" s="15" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="L172" s="3" t="s">
         <v>468</v>
@@ -12466,39 +12492,39 @@
       </c>
       <c r="O172" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "BofM", "bookName": "Moroni", "bookSubtitle": "", "bookOsisID": "Moro", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Mni"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0401-01-01", "dateLatest": "0401-01-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Mormon", "bookSubtitle": "", "bookOsisID": "Morm", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Mmn"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0321-01-01", "dateLatest": "0421-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="173" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>564</v>
+        <v>706</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>721</v>
+        <v>1210</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="I173" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="J173" s="12" t="s">
-        <v>1176</v>
-      </c>
-      <c r="K173" s="12" t="s">
-        <v>1179</v>
+      <c r="J173" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="K173" s="15" t="s">
+        <v>603</v>
       </c>
       <c r="L173" s="3" t="s">
         <v>468</v>
@@ -12512,39 +12538,36 @@
       </c>
       <c r="O173" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "PGP", "bookName": "Moses", "bookSubtitle": "Selections from the Book of Moses", "bookOsisID": "Mos", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["The Book of Moses"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Moses"], "dateEarliest": "1830-06-01", "dateLatest": "1831-02-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Ether", "bookSubtitle": "The record of the Jaredites, taken from the twenty-four plates found by the people of Limhi in the days of King Mosiah.", "bookOsisID": "Eth", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Ethr"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "-2200-01-01", "dateLatest": "-0350-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="174" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>565</v>
+        <v>433</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I174" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="J174" s="12" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K174" s="12" t="s">
-        <v>1180</v>
+      <c r="J174" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="K174" s="15" t="s">
+        <v>604</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>468</v>
@@ -12558,42 +12581,45 @@
       </c>
       <c r="O174" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "PGP", "bookName": "Abraham", "bookSubtitle": "Translated from the Papyrus, by Joseph Smith", "bookOsisID": "Abr", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["The Book of Abraham"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Abraham"], "dateEarliest": "1835-07-01", "dateLatest": "1842-07-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "BofM", "bookName": "Moroni", "bookSubtitle": "", "bookOsisID": "Moro", "paratext": null, "groups": ["Book of Mormon", "LDS", "Mormon", "Large Plates of Nephi", "Abridgement"], "aliases": ["Mni"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Mormon"], "dateEarliest": "0401-01-01", "dateLatest": "0401-01-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="175" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>464</v>
+        <v>721</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>479</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="I175" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J175" s="12" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="K175" s="12" t="s">
-        <v>1178</v>
+        <v>1179</v>
+      </c>
+      <c r="L175" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="M175" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N175" s="3" t="str">
         <f t="shared" si="14"/>
@@ -12601,39 +12627,42 @@
       </c>
       <c r="O175" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "PGP", "bookName": "Articles of Faith", "bookSubtitle": "of The Church of Jesus Christ of Latter-day Saints", "bookOsisID": "AofF", "paratext": null, "groups": ["Pearl of Great Price", "LDS", "Joseph Smith"], "aliases": ["AofF"], "chapterLabel": "", "verseLabel": "Article", "authors": ["Joseph Smith"], "dateEarliest": "1842-03-01", "dateLatest": "1842-03-01", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "PGP", "bookName": "Moses", "bookSubtitle": "Selections from the Book of Moses", "bookOsisID": "Mos", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["The Book of Moses"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Moses"], "dateEarliest": "1830-06-01", "dateLatest": "1831-02-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="176" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>571</v>
+        <v>444</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>479</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I176" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>1181</v>
+        <v>1180</v>
+      </c>
+      <c r="L176" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="M176" s="3" t="s">
         <v>471</v>
@@ -12644,42 +12673,42 @@
       </c>
       <c r="O176" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "PGP", "bookName": "Joseph Smith—History", "bookSubtitle": "Extracts from the History of Joseph Smith, the Prophet", "bookOsisID": "JSH", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["JSH", "JS-H", "Joseph Smith History","Joseph Smith--History"], "chapterLabel": "", "verseLabel": "Verse", "authors": ["Joseph Smith"], "dateEarliest": "1838-04-01", "dateLatest": "1838-04-30", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "PGP", "bookName": "Abraham", "bookSubtitle": "Translated from the Papyrus, by Joseph Smith", "bookOsisID": "Abr", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["The Book of Abraham"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Abraham"], "dateEarliest": "1835-07-01", "dateLatest": "1842-07-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="177" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>572</v>
+        <v>446</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>724</v>
+        <v>464</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>479</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="I177" s="6" t="s">
         <v>744</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="K177" s="12" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="M177" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N177" s="3" t="str">
         <f t="shared" si="14"/>
@@ -12687,27 +12716,27 @@
       </c>
       <c r="O177" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "PGP", "bookName": "Joseph Smith—Matthew", "bookSubtitle": "An extract from the translation of the Bible as revealed to Joseph Smith the Prophet in 1831: Matthew 23:39 and chapter 24", "bookOsisID": "JSM", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["JSM","JS-M",  "Joseph Smith Matthew","Joseph Smith--Matthew"], "chapterLabel": "", "verseLabel": "Verse", "authors": ["St. Matthew"], "dateEarliest": "1831-03-07", "dateLatest": "1831-03-10", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "PGP", "bookName": "Articles of Faith", "bookSubtitle": "of The Church of Jesus Christ of Latter-day Saints", "bookOsisID": "AofF", "paratext": null, "groups": ["Pearl of Great Price", "LDS", "Joseph Smith"], "aliases": ["AofF"], "chapterLabel": "", "verseLabel": "Article", "authors": ["Joseph Smith"], "dateEarliest": "1842-03-01", "dateLatest": "1842-03-01", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="178" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>451</v>
+        <v>571</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>570</v>
+        <v>461</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>638</v>
+        <v>723</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="H178" s="6" t="s">
         <v>667</v>
@@ -12715,14 +12744,11 @@
       <c r="I178" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="J178" s="15" t="s">
-        <v>1153</v>
-      </c>
-      <c r="K178" s="15" t="s">
-        <v>1154</v>
-      </c>
-      <c r="L178" s="3" t="s">
-        <v>469</v>
+      <c r="J178" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K178" s="12" t="s">
+        <v>1181</v>
       </c>
       <c r="M178" s="3" t="s">
         <v>471</v>
@@ -12733,152 +12759,213 @@
       </c>
       <c r="O178" s="3" t="str">
         <f t="shared" si="11"/>
+        <v>{ "workOsisID": "PGP", "bookName": "Joseph Smith—History", "bookSubtitle": "Extracts from the History of Joseph Smith, the Prophet", "bookOsisID": "JSH", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["JSH", "JS-H", "Joseph Smith History","Joseph Smith--History"], "chapterLabel": "", "verseLabel": "Verse", "authors": ["Joseph Smith"], "dateEarliest": "1838-04-01", "dateLatest": "1838-04-30", "hasData": true, "traditions": ["lds"] },</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="K179" s="12" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M179" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N179" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>true</v>
+      </c>
+      <c r="O179" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>{ "workOsisID": "PGP", "bookName": "Joseph Smith—Matthew", "bookSubtitle": "An extract from the translation of the Bible as revealed to Joseph Smith the Prophet in 1831: Matthew 23:39 and chapter 24", "bookOsisID": "JSM", "paratext": null, "groups": ["Pearl of Great Price", "Inspired Translation", "Joseph Smith Translation", "JST", "Joseph Smith", "LDS"], "aliases": ["JSM","JS-M",  "Joseph Smith Matthew","Joseph Smith--Matthew"], "chapterLabel": "", "verseLabel": "Verse", "authors": ["St. Matthew"], "dateEarliest": "1831-03-07", "dateLatest": "1831-03-10", "hasData": true, "traditions": ["lds"] },</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="J180" s="15" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K180" s="15" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L180" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="M180" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N180" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>true</v>
+      </c>
+      <c r="O180" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>{ "workOsisID": "D&amp;C", "bookName": "D&amp;C", "bookSubtitle": "of The Church of Jesus Christ of Latter-day Saints", "bookOsisID": "D&amp;C", "paratext": null, "groups": ["Doctrine and Covenants","LDS"], "aliases": ["D and C", "The Doctrine &amp; Covenants","Doctrine &amp; Covenants", "The Doctrine and Covenants"], "chapterLabel": "Section", "verseLabel": "Verse", "authors": ["Joseph Smith"], "dateEarliest": "1823-09-21", "dateLatest": "1841-01-19", "hasData": true, "traditions": ["lds"] },</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
-        <v>634</v>
-      </c>
-      <c r="I179" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J179" s="14" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K179" s="14" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>605</v>
-      </c>
-      <c r="I180" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J180" s="14" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K180" s="14" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J181" s="14" t="s">
-        <v>1133</v>
+        <v>1078</v>
       </c>
       <c r="K181" s="14" t="s">
-        <v>1010</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J182" s="14" t="s">
-        <v>1133</v>
+        <v>1080</v>
       </c>
       <c r="K182" s="14" t="s">
-        <v>1134</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>1085</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>1008</v>
+        <v>1133</v>
       </c>
       <c r="K183" s="14" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>1085</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>1029</v>
+        <v>1133</v>
       </c>
       <c r="K184" s="14" t="s">
-        <v>1073</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>1085</v>
       </c>
       <c r="J185" s="14" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="K185" s="14" t="s">
-        <v>1082</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>1085</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>1013</v>
+        <v>1029</v>
       </c>
       <c r="K186" s="14" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="K187" s="14" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="J188" s="14" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="K188" s="14" t="s">
-        <v>1022</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>1086</v>
@@ -12887,29 +12974,29 @@
         <v>1021</v>
       </c>
       <c r="K189" s="14" t="s">
-        <v>1019</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="K190" s="14" t="s">
-        <v>1073</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="J191" s="14" t="s">
         <v>1021</v>
@@ -12920,7 +13007,7 @@
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>1087</v>
@@ -12929,46 +13016,46 @@
         <v>1032</v>
       </c>
       <c r="K192" s="14" t="s">
-        <v>1019</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>1087</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="K193" s="14" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>583</v>
+        <v>1032</v>
       </c>
       <c r="K194" s="14" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="J195" s="14" t="s">
-        <v>1135</v>
+        <v>1014</v>
       </c>
       <c r="K195" s="14" t="s">
         <v>1017</v>
@@ -12976,188 +13063,216 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>1136</v>
+        <v>583</v>
       </c>
       <c r="K196" s="14" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>1006</v>
+        <v>1135</v>
       </c>
       <c r="K197" s="14" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>1089</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K198" s="14" t="s">
-        <v>1138</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>1032</v>
+        <v>1006</v>
       </c>
       <c r="K199" s="14" t="s">
-        <v>1139</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="K200" s="14" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="J201" s="14" t="s">
-        <v>1142</v>
+        <v>1032</v>
       </c>
       <c r="K201" s="14" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="J202" s="14" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="K202" s="14" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>1091</v>
       </c>
       <c r="J203" s="14" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="K203" s="14" t="s">
-        <v>1107</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="K204" s="14" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="K205" s="14" t="s">
-        <v>1149</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>1092</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="K206" s="14" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="J207" s="14" t="s">
         <v>1148</v>
       </c>
       <c r="K207" s="14" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>631</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="J208" s="14" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K208" s="14" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>632</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="J209" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K209" s="14" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
         <v>633</v>
       </c>
-      <c r="I208" s="7" t="s">
+      <c r="I210" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="J208" s="14" t="s">
+      <c r="J210" s="14" t="s">
         <v>1152</v>
       </c>
-      <c r="K208" s="14" t="s">
+      <c r="K210" s="14" t="s">
         <v>1134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E178" xr:uid="{2457BBF2-065A-6B4B-8450-DD145766C676}"/>
+  <autoFilter ref="A1:E180" xr:uid="{2457BBF2-065A-6B4B-8450-DD145766C676}"/>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" location="cite_note-6" display="https://wiki.crosswire.org/OSIS_Book_Abbreviations - cite_note-6" xr:uid="{413E20E8-A50F-EA4D-8B77-20FFD74AB053}"/>
   </hyperlinks>
@@ -13322,7 +13437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666CD579-589B-8442-BE20-716F9EAF0623}">
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -13399,7 +13514,7 @@
         <v>true</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I9" si="1">"{ ""workOsisID"": """&amp;B3&amp;""", ""workTitle"": """&amp;C3&amp;""", ""workSubtitle"": """&amp;D3&amp;""", ""aliases"": "&amp;E3&amp;", ""hasData"": "&amp;H3&amp;" },"</f>
+        <f t="shared" ref="I3:I11" si="1">"{ ""workOsisID"": """&amp;B3&amp;""", ""workTitle"": """&amp;C3&amp;""", ""workSubtitle"": """&amp;D3&amp;""", ""aliases"": "&amp;E3&amp;", ""hasData"": "&amp;H3&amp;" },"</f>
         <v>{ "workOsisID": "KJVA", "workTitle": "The Holy Bible Apocrypha", "workSubtitle": "King James Version", "aliases": ["King James Apocrypha"], "hasData": true },</v>
       </c>
     </row>
@@ -13530,6 +13645,45 @@
       <c r="I9" t="str">
         <f t="shared" si="1"/>
         <v>{ "workOsisID": "Fathers", "workTitle": "Apostolic Fathers", "workSubtitle": "Translated by J.  B. Lightfoot", "aliases": ["The Apostolic Fathers"], "hasData": false },</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>{ "workOsisID": "Jasher", "workTitle": "Jasher", "workSubtitle": "", "aliases": ["Sepir Ha Yasher","Sefer haYashar","The Book of Jasher","Book of Jasher"], "hasData": true },</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v>{ "workOsisID": "AscIsa", "workTitle": "Ascension of Isaiah", "workSubtitle": "Translated by R. H. Charles", "aliases": ["The Ascension of Isaiah"], "hasData": true },</v>
       </c>
     </row>
   </sheetData>

--- a/data/research/research.xlsx
+++ b/data/research/research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksnyder/Sites/public-domain-books/data/research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B540EFB-3EAF-C94B-BBE0-DEC8ABB7AFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD84B17-0A10-574F-808B-CE58F04C01AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19420" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
+    <workbookView xWindow="53100" yWindow="700" windowWidth="47220" windowHeight="25960" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1304">
   <si>
     <t>Gen</t>
   </si>
@@ -3952,6 +3952,9 @@
   </si>
   <si>
     <t>["Song of the Three Children","Song of the Three Holy Children","Aza"]</t>
+  </si>
+  <si>
+    <t>["D and C","The Doctrine &amp; Covenants","Doctrine &amp; Covenants", "The Doctrine and Covenants"]</t>
   </si>
 </sst>
 </file>
@@ -12807,7 +12810,7 @@
     </row>
     <row r="180" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>451</v>
+        <v>568</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>567</v>
@@ -12819,7 +12822,7 @@
         <v>569</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>637</v>
+        <v>1303</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>451</v>
@@ -12848,7 +12851,7 @@
       </c>
       <c r="O180" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "D&amp;C", "bookName": "D&amp;C", "bookSubtitle": "of The Church of Jesus Christ of Latter-day Saints", "bookOsisID": "D&amp;C", "paratext": null, "groups": ["Doctrine and Covenants","LDS"], "aliases": ["D and C", "The Doctrine &amp; Covenants","Doctrine &amp; Covenants", "The Doctrine and Covenants"], "chapterLabel": "Section", "verseLabel": "Verse", "authors": ["Joseph Smith"], "dateEarliest": "1823-09-21", "dateLatest": "1841-01-19", "hasData": true, "traditions": ["lds"] },</v>
+        <v>{ "workOsisID": "D&amp;C", "bookName": "Doctrine and Covenants", "bookSubtitle": "of The Church of Jesus Christ of Latter-day Saints", "bookOsisID": "D&amp;C", "paratext": null, "groups": ["Doctrine and Covenants","LDS"], "aliases": ["D and C","The Doctrine &amp; Covenants","Doctrine &amp; Covenants", "The Doctrine and Covenants"], "chapterLabel": "Section", "verseLabel": "Verse", "authors": ["Joseph Smith"], "dateEarliest": "1823-09-21", "dateLatest": "1841-01-19", "hasData": true, "traditions": ["lds"] },</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.2">

--- a/data/research/research.xlsx
+++ b/data/research/research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksnyder/Sites/public-domain-books/data/research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD84B17-0A10-574F-808B-CE58F04C01AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8E7382-B583-6240-AB50-CC95BFC6331F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="53100" yWindow="700" windowWidth="47220" windowHeight="25960" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="1303">
   <si>
     <t>Gen</t>
   </si>
@@ -3532,9 +3532,6 @@
   </si>
   <si>
     <t>03-10-1831</t>
-  </si>
-  <si>
-    <t>Academic</t>
   </si>
   <si>
     <t>Enoch</t>
@@ -4494,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>641</v>
@@ -4543,10 +4540,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>476</v>
@@ -4592,7 +4589,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>642</v>
@@ -4641,7 +4638,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>643</v>
@@ -4690,10 +4687,10 @@
         <v>14</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>476</v>
@@ -4740,10 +4737,10 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>476</v>
@@ -4790,10 +4787,10 @@
         <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>476</v>
@@ -4840,7 +4837,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>644</v>
@@ -4890,10 +4887,10 @@
         <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>476</v>
@@ -4940,10 +4937,10 @@
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>476</v>
@@ -4989,10 +4986,10 @@
         <v>31</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>476</v>
@@ -5038,10 +5035,10 @@
         <v>34</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>476</v>
@@ -5087,10 +5084,10 @@
         <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>476</v>
@@ -5136,10 +5133,10 @@
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>476</v>
@@ -5186,7 +5183,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>721</v>
@@ -5236,10 +5233,10 @@
         <v>45</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>476</v>
@@ -5286,7 +5283,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>722</v>
@@ -5336,10 +5333,10 @@
         <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>476</v>
@@ -5386,10 +5383,10 @@
         <v>52</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>476</v>
@@ -5436,10 +5433,10 @@
         <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>476</v>
@@ -5486,10 +5483,10 @@
         <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>476</v>
@@ -5536,10 +5533,10 @@
         <v>61</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>476</v>
@@ -5586,10 +5583,10 @@
         <v>64</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>476</v>
@@ -5636,10 +5633,10 @@
         <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>476</v>
@@ -5686,10 +5683,10 @@
         <v>70</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>476</v>
@@ -5736,10 +5733,10 @@
         <v>73</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>476</v>
@@ -5786,7 +5783,7 @@
         <v>76</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>730</v>
@@ -5836,10 +5833,10 @@
         <v>79</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>476</v>
@@ -5886,10 +5883,10 @@
         <v>81</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>476</v>
@@ -5936,7 +5933,7 @@
         <v>83</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>731</v>
@@ -5986,10 +5983,10 @@
         <v>86</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>476</v>
@@ -6036,10 +6033,10 @@
         <v>88</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>476</v>
@@ -6086,10 +6083,10 @@
         <v>91</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>476</v>
@@ -6136,10 +6133,10 @@
         <v>94</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>476</v>
@@ -6186,10 +6183,10 @@
         <v>97</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>476</v>
@@ -6236,10 +6233,10 @@
         <v>100</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>476</v>
@@ -6286,10 +6283,10 @@
         <v>103</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>476</v>
@@ -6336,10 +6333,10 @@
         <v>106</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>476</v>
@@ -6386,10 +6383,10 @@
         <v>109</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>476</v>
@@ -6435,7 +6432,7 @@
         <v>112</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>698</v>
@@ -6484,10 +6481,10 @@
         <v>114</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>476</v>
@@ -6533,7 +6530,7 @@
         <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>699</v>
@@ -6582,10 +6579,10 @@
         <v>118</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>476</v>
@@ -6631,7 +6628,7 @@
         <v>120</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>732</v>
@@ -6680,7 +6677,7 @@
         <v>123</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>733</v>
@@ -6729,10 +6726,10 @@
         <v>126</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>476</v>
@@ -6778,10 +6775,10 @@
         <v>129</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>476</v>
@@ -6827,7 +6824,7 @@
         <v>132</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>734</v>
@@ -6876,7 +6873,7 @@
         <v>135</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>735</v>
@@ -6925,10 +6922,10 @@
         <v>138</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>476</v>
@@ -6974,7 +6971,7 @@
         <v>141</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>736</v>
@@ -7023,10 +7020,10 @@
         <v>144</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>476</v>
@@ -7072,10 +7069,10 @@
         <v>147</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>476</v>
@@ -7121,10 +7118,10 @@
         <v>150</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>476</v>
@@ -7170,10 +7167,10 @@
         <v>153</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>476</v>
@@ -7219,7 +7216,7 @@
         <v>155</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>737</v>
@@ -7268,10 +7265,10 @@
         <v>158</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>476</v>
@@ -7317,7 +7314,7 @@
         <v>161</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>667</v>
@@ -7366,10 +7363,10 @@
         <v>164</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>476</v>
@@ -7415,10 +7412,10 @@
         <v>167</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>476</v>
@@ -7464,10 +7461,10 @@
         <v>170</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>476</v>
@@ -7513,10 +7510,10 @@
         <v>173</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>476</v>
@@ -7562,10 +7559,10 @@
         <v>176</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>476</v>
@@ -7611,10 +7608,10 @@
         <v>179</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>476</v>
@@ -7660,10 +7657,10 @@
         <v>181</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>476</v>
@@ -7709,7 +7706,7 @@
         <v>184</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>738</v>
@@ -7762,7 +7759,7 @@
         <v>453</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>475</v>
@@ -7812,7 +7809,7 @@
         <v>453</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>475</v>
@@ -7904,7 +7901,7 @@
         <v>453</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>475</v>
@@ -8051,7 +8048,7 @@
         <v>453</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>475</v>
@@ -8075,7 +8072,7 @@
         <v>470</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O74" s="3" t="str">
         <f t="shared" si="4"/>
@@ -8099,7 +8096,7 @@
         <v>453</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>475</v>
@@ -8231,7 +8228,7 @@
         <v>453</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>475</v>
@@ -8376,7 +8373,7 @@
         <v>453</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>475</v>
@@ -8425,7 +8422,7 @@
         <v>453</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>475</v>
@@ -8474,7 +8471,7 @@
         <v>453</v>
       </c>
       <c r="F83" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H83" t="s">
         <v>667</v>
@@ -8520,7 +8517,7 @@
         <v>453</v>
       </c>
       <c r="F84" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H84" t="s">
         <v>667</v>
@@ -8566,7 +8563,7 @@
         <v>453</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>475</v>
@@ -8615,7 +8612,7 @@
         <v>453</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>475</v>
@@ -8664,7 +8661,7 @@
         <v>453</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>475</v>
@@ -9124,7 +9121,7 @@
         <v>454</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>475</v>
@@ -9173,7 +9170,7 @@
         <v>667</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H98" t="s">
         <v>693</v>
@@ -9219,7 +9216,7 @@
         <v>709</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H99" t="s">
         <v>693</v>
@@ -9265,7 +9262,7 @@
         <v>667</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H100" t="s">
         <v>693</v>
@@ -9311,7 +9308,7 @@
         <v>667</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H101" t="s">
         <v>670</v>
@@ -9357,7 +9354,7 @@
         <v>667</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H102" t="s">
         <v>649</v>
@@ -9397,13 +9394,13 @@
         <v>278</v>
       </c>
       <c r="E103" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F103" t="s">
         <v>710</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H103" t="s">
         <v>694</v>
@@ -9443,7 +9440,7 @@
         <v>281</v>
       </c>
       <c r="E104" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F104" t="s">
         <v>667</v>
@@ -9486,7 +9483,7 @@
         <v>284</v>
       </c>
       <c r="E105" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F105" t="s">
         <v>711</v>
@@ -9529,7 +9526,7 @@
         <v>286</v>
       </c>
       <c r="E106" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F106" t="s">
         <v>667</v>
@@ -9572,7 +9569,7 @@
         <v>288</v>
       </c>
       <c r="E107" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F107" t="s">
         <v>667</v>
@@ -9615,7 +9612,7 @@
         <v>290</v>
       </c>
       <c r="E108" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F108" t="s">
         <v>667</v>
@@ -9658,7 +9655,7 @@
         <v>292</v>
       </c>
       <c r="E109" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F109" t="s">
         <v>712</v>
@@ -9698,7 +9695,7 @@
         <v>293</v>
       </c>
       <c r="E110" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F110" t="s">
         <v>713</v>
@@ -9738,7 +9735,7 @@
         <v>295</v>
       </c>
       <c r="E111" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F111" t="s">
         <v>714</v>
@@ -9781,7 +9778,7 @@
         <v>297</v>
       </c>
       <c r="E112" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F112" t="s">
         <v>667</v>
@@ -9824,7 +9821,7 @@
         <v>300</v>
       </c>
       <c r="E113" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F113" t="s">
         <v>667</v>
@@ -9867,7 +9864,7 @@
         <v>302</v>
       </c>
       <c r="E114" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F114" t="s">
         <v>667</v>
@@ -9910,7 +9907,7 @@
         <v>304</v>
       </c>
       <c r="E115" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F115" t="s">
         <v>667</v>
@@ -9953,7 +9950,7 @@
         <v>306</v>
       </c>
       <c r="E116" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F116" t="s">
         <v>667</v>
@@ -9993,7 +9990,7 @@
         <v>307</v>
       </c>
       <c r="E117" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F117" t="s">
         <v>667</v>
@@ -10027,19 +10024,19 @@
     </row>
     <row r="118" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>1237</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>1238</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>525</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>309</v>
@@ -10063,7 +10060,7 @@
         <v>470</v>
       </c>
       <c r="N118" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O118" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10072,19 +10069,19 @@
     </row>
     <row r="119" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>1241</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>1242</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>526</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>309</v>
@@ -10108,7 +10105,7 @@
         <v>470</v>
       </c>
       <c r="N119" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O119" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10117,19 +10114,19 @@
     </row>
     <row r="120" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>1231</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>1232</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>527</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>309</v>
@@ -10153,7 +10150,7 @@
         <v>470</v>
       </c>
       <c r="N120" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O120" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10162,19 +10159,19 @@
     </row>
     <row r="121" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>1235</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>1236</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>528</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>309</v>
@@ -10198,7 +10195,7 @@
         <v>470</v>
       </c>
       <c r="N121" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O121" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10207,19 +10204,19 @@
     </row>
     <row r="122" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>1227</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>1228</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>529</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>309</v>
@@ -10243,7 +10240,7 @@
         <v>470</v>
       </c>
       <c r="N122" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O122" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10252,19 +10249,19 @@
     </row>
     <row r="123" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>1239</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>1240</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>530</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>309</v>
@@ -10288,7 +10285,7 @@
         <v>470</v>
       </c>
       <c r="N123" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O123" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10297,19 +10294,19 @@
     </row>
     <row r="124" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>1225</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>1226</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>531</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>309</v>
@@ -10333,7 +10330,7 @@
         <v>470</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O124" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10342,19 +10339,19 @@
     </row>
     <row r="125" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>1223</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>1224</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>532</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>309</v>
@@ -10378,7 +10375,7 @@
         <v>470</v>
       </c>
       <c r="N125" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O125" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10387,19 +10384,19 @@
     </row>
     <row r="126" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>1233</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>1234</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>533</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>309</v>
@@ -10423,7 +10420,7 @@
         <v>470</v>
       </c>
       <c r="N126" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O126" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10432,19 +10429,19 @@
     </row>
     <row r="127" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>1219</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>1220</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>534</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>309</v>
@@ -10468,7 +10465,7 @@
         <v>470</v>
       </c>
       <c r="N127" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O127" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10477,19 +10474,19 @@
     </row>
     <row r="128" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>1221</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>1222</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>535</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>309</v>
@@ -10513,7 +10510,7 @@
         <v>470</v>
       </c>
       <c r="N128" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O128" s="3" t="str">
         <f t="shared" si="4"/>
@@ -10522,19 +10519,19 @@
     </row>
     <row r="129" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>1229</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>1230</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>536</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>309</v>
@@ -10558,7 +10555,7 @@
         <v>470</v>
       </c>
       <c r="N129" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O129" s="3" t="str">
         <f t="shared" si="4"/>
@@ -11762,13 +11759,10 @@
         <v>375</v>
       </c>
       <c r="E156" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F156" t="s">
         <v>441</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>1163</v>
       </c>
       <c r="H156" t="s">
         <v>782</v>
@@ -11794,24 +11788,24 @@
       </c>
       <c r="O156" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "Academic", "bookName": "Diatessaron", "bookSubtitle": "", "bookOsisID": "TatDiat", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Tatian's Diatessaron","Tatian"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Tatian"], "dateEarliest": "0160-01-01", "dateLatest": "0175-12-31", "hasData": false, "traditions": ["academic"] },</v>
+        <v>{ "workOsisID": "", "bookName": "Diatessaron", "bookSubtitle": "", "bookOsisID": "TatDiat", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Tatian's Diatessaron","Tatian"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Tatian"], "dateEarliest": "0160-01-01", "dateLatest": "0175-12-31", "hasData": false, "traditions": ["academic"] },</v>
       </c>
     </row>
     <row r="157" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F157" s="20" t="s">
         <v>1261</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>1261</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="F157" s="20" t="s">
-        <v>1262</v>
-      </c>
       <c r="G157" s="6" t="s">
-        <v>1163</v>
+        <v>1260</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>647</v>
@@ -11820,11 +11814,11 @@
         <v>760</v>
       </c>
       <c r="J157" s="16" t="s">
+        <v>1262</v>
+      </c>
+      <c r="K157" s="16" t="s">
         <v>1263</v>
       </c>
-      <c r="K157" s="16" t="s">
-        <v>1264</v>
-      </c>
       <c r="L157" s="3" t="s">
         <v>467</v>
       </c>
@@ -11832,28 +11826,28 @@
         <v>470</v>
       </c>
       <c r="N157" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O157" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "Academic", "bookName": "Jasher", "bookSubtitle": "", "bookOsisID": "Jasher", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Sepir Ha Yasher","Sefer haYashar","The Book of Jasher","Book of Jasher"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Moses"], "dateEarliest": "1200-01-01", "dateLatest": "1300-01-01", "hasData": true, "traditions": ["academic"] },</v>
+        <v>{ "workOsisID": "Jasher", "bookName": "Jasher", "bookSubtitle": "", "bookOsisID": "Jasher", "paratext": null, "groups": ["Apocrypha"], "aliases": ["Sepir Ha Yasher","Sefer haYashar","The Book of Jasher","Book of Jasher"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Moses"], "dateEarliest": "1200-01-01", "dateLatest": "1300-01-01", "hasData": true, "traditions": ["academic"] },</v>
       </c>
     </row>
     <row r="158" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E158" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C158" s="3" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E158" s="3" t="s">
+      <c r="F158" s="20" t="s">
         <v>1266</v>
       </c>
-      <c r="F158" s="20" t="s">
-        <v>1267</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>1163</v>
+      <c r="G158" s="3" t="s">
+        <v>1268</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>648</v>
@@ -11865,7 +11859,7 @@
         <v>1126</v>
       </c>
       <c r="K158" s="16" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="L158" s="3" t="s">
         <v>467</v>
@@ -11874,11 +11868,11 @@
         <v>470</v>
       </c>
       <c r="N158" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="O158" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "Academic", "bookName": "Ascension of Isaiah", "bookSubtitle": "", "bookOsisID": "AscIsa", "paratext": null, "groups": ["Apocrypha"], "aliases": ["The Ascension of Isaiah"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Isaiah"], "dateEarliest": "0150-01-01", "dateLatest": "0200-01-01", "hasData": true, "traditions": ["academic"] },</v>
+        <v>{ "workOsisID": "AscIsa", "bookName": "Ascension of Isaiah", "bookSubtitle": "", "bookOsisID": "AscIsa", "paratext": null, "groups": ["Apocrypha"], "aliases": ["The Ascension of Isaiah"], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": ["Isaiah"], "dateEarliest": "0150-01-01", "dateLatest": "0200-01-01", "hasData": true, "traditions": ["academic"] },</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.2">
@@ -11897,9 +11891,6 @@
       <c r="F159" t="s">
         <v>667</v>
       </c>
-      <c r="G159" s="7" t="s">
-        <v>1163</v>
-      </c>
       <c r="H159" s="7" t="s">
         <v>667</v>
       </c>
@@ -11924,7 +11915,7 @@
       </c>
       <c r="O159" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>{ "workOsisID": "Academic", "bookName": "Metrical Psalms", "bookSubtitle": "", "bookOsisID": "PsMet", "paratext": "PSB", "groups": ["Apocrypha", "Apocrypha"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": [], "dateEarliest": "0160-01-01", "dateLatest": "0180-12-31", "hasData": false, "traditions": ["academic"] },</v>
+        <v>{ "workOsisID": "", "bookName": "Metrical Psalms", "bookSubtitle": "", "bookOsisID": "PsMet", "paratext": "PSB", "groups": ["Apocrypha", "Apocrypha"], "aliases": [], "chapterLabel": "Chapter", "verseLabel": "Verse", "authors": [], "dateEarliest": "0160-01-01", "dateLatest": "0180-12-31", "hasData": false, "traditions": ["academic"] },</v>
       </c>
     </row>
     <row r="160" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -12377,7 +12368,7 @@
         <v>460</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G170" s="6" t="s">
         <v>477</v>
@@ -12423,7 +12414,7 @@
         <v>460</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G171" s="6" t="s">
         <v>477</v>
@@ -12512,7 +12503,7 @@
         <v>460</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>477</v>
@@ -12613,10 +12604,10 @@
         <v>740</v>
       </c>
       <c r="J175" s="12" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="K175" s="12" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L175" s="3" t="s">
         <v>467</v>
@@ -12659,10 +12650,10 @@
         <v>740</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L176" s="3" t="s">
         <v>467</v>
@@ -12693,7 +12684,7 @@
         <v>462</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>478</v>
@@ -12705,10 +12696,10 @@
         <v>740</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K177" s="12" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="M177" s="3" t="s">
         <v>471</v>
@@ -12736,7 +12727,7 @@
         <v>461</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>478</v>
@@ -12748,10 +12739,10 @@
         <v>740</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="K178" s="12" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="M178" s="3" t="s">
         <v>470</v>
@@ -12779,7 +12770,7 @@
         <v>461</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G179" s="6" t="s">
         <v>478</v>
@@ -12791,10 +12782,10 @@
         <v>740</v>
       </c>
       <c r="J179" s="12" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="K179" s="12" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="M179" s="3" t="s">
         <v>470</v>
@@ -12822,7 +12813,7 @@
         <v>569</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>451</v>
@@ -13291,7 +13282,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B1" t="s">
         <v>311</v>
@@ -13303,7 +13294,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B2" t="s">
         <v>312</v>
@@ -13315,7 +13306,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B3" t="s">
         <v>313</v>
@@ -13327,7 +13318,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B4" t="s">
         <v>314</v>
@@ -13339,7 +13330,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B5" t="s">
         <v>315</v>
@@ -13351,7 +13342,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B6" t="s">
         <v>316</v>
@@ -13363,7 +13354,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B7" t="s">
         <v>317</v>
@@ -13375,7 +13366,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B8" t="s">
         <v>318</v>
@@ -13387,7 +13378,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B9" t="s">
         <v>319</v>
@@ -13399,7 +13390,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B10" t="s">
         <v>320</v>
@@ -13411,7 +13402,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B11" t="s">
         <v>321</v>
@@ -13423,7 +13414,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B12" t="s">
         <v>322</v>
@@ -13532,7 +13523,7 @@
         <v>640</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="1"/>
@@ -13652,16 +13643,16 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E10" t="s">
         <v>1261</v>
       </c>
-      <c r="C10" t="s">
-        <v>1261</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1262</v>
-      </c>
       <c r="H10" s="19" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="1"/>
@@ -13670,19 +13661,19 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D11" t="s">
         <v>1269</v>
       </c>
-      <c r="C11" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1270</v>
-      </c>
       <c r="E11" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="1"/>
